--- a/public/dokumen/Laporan_Validasi_Database.xlsx
+++ b/public/dokumen/Laporan_Validasi_Database.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerjaan\Project\SPTJM_GITHUB\SPTJMv2.lldikti4\public\dokumen\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C71985-8399-4066-A513-F2ACDDA78E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Laporan Validasi DB" sheetId="1" r:id="rId4"/>
+    <sheet name="Laporan Validasi DB" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laporan Validasi DB'!$A$1:$R$493</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4197" uniqueCount="720">
   <si>
     <t>no</t>
   </si>
@@ -2066,9 +2074,6 @@
     <t>Selesai Studi</t>
   </si>
   <si>
-    <t>o</t>
-  </si>
-  <si>
     <t>ILHAM FAJAR SUHENDAR, S.PD., M.PD</t>
   </si>
   <si>
@@ -2145,29 +2150,54 @@
   </si>
   <si>
     <t>20260618_ba_juni_2026.pdf</t>
+  </si>
+  <si>
+    <t>6544752653230160</t>
+  </si>
+  <si>
+    <t>3248761661300000</t>
+  </si>
+  <si>
+    <t>2460764665230230</t>
+  </si>
+  <si>
+    <t>3674030312640000</t>
+  </si>
+  <si>
+    <t>2050765666230340</t>
+  </si>
+  <si>
+    <t>6660750651130070</t>
+  </si>
+  <si>
+    <t>6940770671230300</t>
+  </si>
+  <si>
+    <t>4041758659130170</t>
+  </si>
+  <si>
+    <t>2953766667130260</t>
+  </si>
+  <si>
+    <t>2747769670130400</t>
+  </si>
+  <si>
+    <t>1557753654230180</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -2199,19 +2229,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="49" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="14" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2499,36 +2536,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:T493"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R493"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="true" style="0"/>
-    <col min="2" max="2" width="11" customWidth="true" style="3"/>
-    <col min="3" max="3" width="17.28515625" customWidth="true" style="3"/>
-    <col min="4" max="4" width="49.7109375" customWidth="true" style="0"/>
-    <col min="5" max="5" width="67.5703125" customWidth="true" style="0"/>
-    <col min="6" max="6" width="8.28515625" customWidth="true" style="3"/>
-    <col min="7" max="7" width="18.42578125" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.42578125" customWidth="true" style="0"/>
-    <col min="9" max="9" width="34.28515625" customWidth="true" style="0"/>
-    <col min="10" max="10" width="9.7109375" customWidth="true" style="0"/>
-    <col min="11" max="11" width="23.140625" customWidth="true" style="0"/>
-    <col min="12" max="12" width="18.42578125" customWidth="true" style="0"/>
-    <col min="13" max="13" width="18.42578125" customWidth="true" style="0"/>
-    <col min="14" max="14" width="30.85546875" customWidth="true" style="0"/>
-    <col min="15" max="15" width="131.5703125" customWidth="true" style="0"/>
-    <col min="16" max="16" width="22.7109375" customWidth="true" style="0"/>
-    <col min="17" max="17" width="10.42578125" customWidth="true" style="0"/>
-    <col min="18" max="18" width="11.140625" customWidth="true" style="0"/>
-    <col min="19" max="19" width="17" customWidth="true" style="0"/>
-    <col min="20" max="20" width="50" customWidth="true" style="0"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="49.7109375" customWidth="1"/>
+    <col min="5" max="5" width="67.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="34.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="12" max="13" width="18.42578125" customWidth="1"/>
+    <col min="14" max="14" width="30.85546875" customWidth="1"/>
+    <col min="15" max="15" width="131.5703125" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2584,7 +2617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
@@ -2609,8 +2642,7 @@
       <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="J2"/>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>46146</v>
       </c>
       <c r="O2" t="s">
@@ -2620,7 +2652,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
@@ -2645,7 +2677,6 @@
       <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="J3"/>
       <c r="M3" t="s">
         <v>27</v>
       </c>
@@ -2659,7 +2690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>36</v>
       </c>
@@ -2684,7 +2715,6 @@
       <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="J4"/>
       <c r="M4" t="s">
         <v>27</v>
       </c>
@@ -2698,7 +2728,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>40</v>
       </c>
@@ -2723,7 +2753,6 @@
       <c r="I5" t="s">
         <v>25</v>
       </c>
-      <c r="J5"/>
       <c r="M5" t="s">
         <v>27</v>
       </c>
@@ -2737,7 +2766,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>47</v>
       </c>
@@ -2759,7 +2788,6 @@
       <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="J6"/>
       <c r="M6" t="s">
         <v>27</v>
       </c>
@@ -2773,7 +2801,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>53</v>
       </c>
@@ -2798,7 +2826,6 @@
       <c r="I7" t="s">
         <v>25</v>
       </c>
-      <c r="J7"/>
       <c r="M7" t="s">
         <v>27</v>
       </c>
@@ -2812,7 +2839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
@@ -2837,7 +2864,6 @@
       <c r="I8" t="s">
         <v>25</v>
       </c>
-      <c r="J8"/>
       <c r="M8" t="s">
         <v>27</v>
       </c>
@@ -2851,7 +2877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
@@ -2876,7 +2902,6 @@
       <c r="I9" t="s">
         <v>25</v>
       </c>
-      <c r="J9"/>
       <c r="M9" t="s">
         <v>66</v>
       </c>
@@ -2890,7 +2915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2915,7 +2940,6 @@
       <c r="I10" t="s">
         <v>25</v>
       </c>
-      <c r="J10"/>
       <c r="M10" t="s">
         <v>66</v>
       </c>
@@ -2929,7 +2953,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>74</v>
       </c>
@@ -2954,7 +2978,6 @@
       <c r="I11" t="s">
         <v>25</v>
       </c>
-      <c r="J11"/>
       <c r="M11" t="s">
         <v>66</v>
       </c>
@@ -2968,7 +2991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>78</v>
       </c>
@@ -2993,7 +3016,6 @@
       <c r="I12" t="s">
         <v>25</v>
       </c>
-      <c r="J12"/>
       <c r="M12" t="s">
         <v>84</v>
       </c>
@@ -3007,7 +3029,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>86</v>
       </c>
@@ -3032,7 +3054,6 @@
       <c r="I13" t="s">
         <v>25</v>
       </c>
-      <c r="J13"/>
       <c r="M13" t="s">
         <v>91</v>
       </c>
@@ -3046,7 +3067,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>93</v>
       </c>
@@ -3071,7 +3092,6 @@
       <c r="I14" t="s">
         <v>25</v>
       </c>
-      <c r="J14"/>
       <c r="M14" t="s">
         <v>91</v>
       </c>
@@ -3085,7 +3105,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>101</v>
       </c>
@@ -3110,7 +3130,6 @@
       <c r="I15" t="s">
         <v>25</v>
       </c>
-      <c r="J15"/>
       <c r="M15" t="s">
         <v>91</v>
       </c>
@@ -3124,7 +3143,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>107</v>
       </c>
@@ -3149,7 +3168,6 @@
       <c r="I16" t="s">
         <v>25</v>
       </c>
-      <c r="J16"/>
       <c r="M16" t="s">
         <v>91</v>
       </c>
@@ -3163,7 +3181,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>114</v>
       </c>
@@ -3188,7 +3206,6 @@
       <c r="I17" t="s">
         <v>25</v>
       </c>
-      <c r="J17"/>
       <c r="M17" t="s">
         <v>119</v>
       </c>
@@ -3202,7 +3219,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>121</v>
       </c>
@@ -3227,7 +3244,6 @@
       <c r="I18" t="s">
         <v>25</v>
       </c>
-      <c r="J18"/>
       <c r="M18" t="s">
         <v>119</v>
       </c>
@@ -3241,7 +3257,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>126</v>
       </c>
@@ -3266,7 +3282,6 @@
       <c r="I19" t="s">
         <v>25</v>
       </c>
-      <c r="J19"/>
       <c r="M19" t="s">
         <v>131</v>
       </c>
@@ -3280,7 +3295,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>133</v>
       </c>
@@ -3305,7 +3320,6 @@
       <c r="I20" t="s">
         <v>25</v>
       </c>
-      <c r="J20"/>
       <c r="M20" t="s">
         <v>131</v>
       </c>
@@ -3319,7 +3333,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>133</v>
       </c>
@@ -3344,7 +3358,6 @@
       <c r="I21" t="s">
         <v>25</v>
       </c>
-      <c r="J21"/>
       <c r="M21" t="s">
         <v>131</v>
       </c>
@@ -3358,7 +3371,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>140</v>
       </c>
@@ -3383,7 +3396,6 @@
       <c r="I22" t="s">
         <v>25</v>
       </c>
-      <c r="J22"/>
       <c r="M22" t="s">
         <v>131</v>
       </c>
@@ -3397,7 +3409,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>144</v>
       </c>
@@ -3422,7 +3434,6 @@
       <c r="I23" t="s">
         <v>25</v>
       </c>
-      <c r="J23"/>
       <c r="M23" t="s">
         <v>150</v>
       </c>
@@ -3436,7 +3447,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>153</v>
       </c>
@@ -3461,7 +3472,6 @@
       <c r="I24" t="s">
         <v>25</v>
       </c>
-      <c r="J24"/>
       <c r="M24" t="s">
         <v>159</v>
       </c>
@@ -3475,7 +3485,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>161</v>
       </c>
@@ -3500,7 +3510,6 @@
       <c r="I25" t="s">
         <v>25</v>
       </c>
-      <c r="J25"/>
       <c r="M25" t="s">
         <v>159</v>
       </c>
@@ -3514,7 +3523,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>168</v>
       </c>
@@ -3539,7 +3548,6 @@
       <c r="I26" t="s">
         <v>25</v>
       </c>
-      <c r="J26"/>
       <c r="M26" t="s">
         <v>171</v>
       </c>
@@ -3553,7 +3561,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>174</v>
       </c>
@@ -3578,7 +3586,6 @@
       <c r="I27" t="s">
         <v>25</v>
       </c>
-      <c r="J27"/>
       <c r="M27" t="s">
         <v>171</v>
       </c>
@@ -3592,7 +3599,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>181</v>
       </c>
@@ -3617,7 +3624,6 @@
       <c r="I28" t="s">
         <v>25</v>
       </c>
-      <c r="J28"/>
       <c r="M28" t="s">
         <v>186</v>
       </c>
@@ -3631,7 +3637,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
@@ -3656,7 +3662,6 @@
       <c r="I29" t="s">
         <v>25</v>
       </c>
-      <c r="J29"/>
       <c r="M29" t="s">
         <v>188</v>
       </c>
@@ -3670,7 +3675,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
@@ -3695,7 +3700,6 @@
       <c r="I30" t="s">
         <v>25</v>
       </c>
-      <c r="J30"/>
       <c r="M30" t="s">
         <v>188</v>
       </c>
@@ -3706,7 +3710,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>196</v>
       </c>
@@ -3728,7 +3732,6 @@
       <c r="I31" t="s">
         <v>25</v>
       </c>
-      <c r="J31"/>
       <c r="M31" t="s">
         <v>201</v>
       </c>
@@ -3742,7 +3745,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>203</v>
       </c>
@@ -3767,7 +3770,6 @@
       <c r="I32" t="s">
         <v>25</v>
       </c>
-      <c r="J32"/>
       <c r="M32" t="s">
         <v>201</v>
       </c>
@@ -3778,7 +3780,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>196</v>
       </c>
@@ -3800,7 +3802,6 @@
       <c r="I33" t="s">
         <v>25</v>
       </c>
-      <c r="J33"/>
       <c r="M33" t="s">
         <v>201</v>
       </c>
@@ -3814,7 +3815,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>78</v>
       </c>
@@ -3839,7 +3840,6 @@
       <c r="I34" t="s">
         <v>25</v>
       </c>
-      <c r="J34"/>
       <c r="M34" t="s">
         <v>201</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>196</v>
       </c>
@@ -3875,7 +3875,6 @@
       <c r="I35" t="s">
         <v>25</v>
       </c>
-      <c r="J35"/>
       <c r="M35" t="s">
         <v>201</v>
       </c>
@@ -3889,7 +3888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>212</v>
       </c>
@@ -3914,7 +3913,6 @@
       <c r="I36" t="s">
         <v>25</v>
       </c>
-      <c r="J36"/>
       <c r="M36" t="s">
         <v>201</v>
       </c>
@@ -3928,7 +3926,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>218</v>
       </c>
@@ -3953,7 +3951,6 @@
       <c r="I37" t="s">
         <v>25</v>
       </c>
-      <c r="J37"/>
       <c r="M37" t="s">
         <v>201</v>
       </c>
@@ -3967,7 +3964,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>222</v>
       </c>
@@ -3992,7 +3989,6 @@
       <c r="I38" t="s">
         <v>25</v>
       </c>
-      <c r="J38"/>
       <c r="M38" t="s">
         <v>201</v>
       </c>
@@ -4006,7 +4002,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>229</v>
       </c>
@@ -4028,7 +4024,6 @@
       <c r="I39" t="s">
         <v>25</v>
       </c>
-      <c r="J39"/>
       <c r="M39" t="s">
         <v>201</v>
       </c>
@@ -4042,7 +4037,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>196</v>
       </c>
@@ -4064,7 +4059,6 @@
       <c r="I40" t="s">
         <v>25</v>
       </c>
-      <c r="J40"/>
       <c r="M40" t="s">
         <v>201</v>
       </c>
@@ -4075,7 +4069,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>203</v>
       </c>
@@ -4100,7 +4094,6 @@
       <c r="I41" t="s">
         <v>25</v>
       </c>
-      <c r="J41"/>
       <c r="M41" t="s">
         <v>201</v>
       </c>
@@ -4111,7 +4104,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>196</v>
       </c>
@@ -4133,7 +4126,6 @@
       <c r="I42" t="s">
         <v>25</v>
       </c>
-      <c r="J42"/>
       <c r="M42" t="s">
         <v>201</v>
       </c>
@@ -4144,7 +4136,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>237</v>
       </c>
@@ -4169,7 +4161,6 @@
       <c r="I43" t="s">
         <v>25</v>
       </c>
-      <c r="J43"/>
       <c r="M43" t="s">
         <v>201</v>
       </c>
@@ -4180,7 +4171,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
         <v>243</v>
       </c>
@@ -4205,7 +4196,6 @@
       <c r="I44" t="s">
         <v>25</v>
       </c>
-      <c r="J44"/>
       <c r="M44" t="s">
         <v>201</v>
       </c>
@@ -4219,7 +4209,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>249</v>
       </c>
@@ -4244,7 +4234,6 @@
       <c r="I45" t="s">
         <v>25</v>
       </c>
-      <c r="J45"/>
       <c r="M45" t="s">
         <v>201</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
         <v>256</v>
       </c>
@@ -4283,7 +4272,6 @@
       <c r="I46" t="s">
         <v>25</v>
       </c>
-      <c r="J46"/>
       <c r="M46" t="s">
         <v>201</v>
       </c>
@@ -4297,7 +4285,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>260</v>
       </c>
@@ -4322,7 +4310,6 @@
       <c r="I47" t="s">
         <v>25</v>
       </c>
-      <c r="J47"/>
       <c r="M47" t="s">
         <v>201</v>
       </c>
@@ -4336,7 +4323,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>266</v>
       </c>
@@ -4361,7 +4348,6 @@
       <c r="I48" t="s">
         <v>25</v>
       </c>
-      <c r="J48"/>
       <c r="M48" t="s">
         <v>201</v>
       </c>
@@ -4375,7 +4361,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>273</v>
       </c>
@@ -4400,7 +4386,6 @@
       <c r="I49" t="s">
         <v>25</v>
       </c>
-      <c r="J49"/>
       <c r="M49" t="s">
         <v>278</v>
       </c>
@@ -4414,7 +4399,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>273</v>
       </c>
@@ -4439,7 +4424,6 @@
       <c r="I50" t="s">
         <v>25</v>
       </c>
-      <c r="J50"/>
       <c r="M50" t="s">
         <v>278</v>
       </c>
@@ -4453,7 +4437,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>281</v>
       </c>
@@ -4475,7 +4459,6 @@
       <c r="I51" t="s">
         <v>25</v>
       </c>
-      <c r="J51"/>
       <c r="M51" t="s">
         <v>278</v>
       </c>
@@ -4489,7 +4472,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>284</v>
       </c>
@@ -4511,7 +4494,6 @@
       <c r="I52" t="s">
         <v>25</v>
       </c>
-      <c r="J52"/>
       <c r="M52" t="s">
         <v>278</v>
       </c>
@@ -4525,7 +4507,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>287</v>
       </c>
@@ -4547,7 +4529,6 @@
       <c r="I53" t="s">
         <v>25</v>
       </c>
-      <c r="J53"/>
       <c r="M53" t="s">
         <v>278</v>
       </c>
@@ -4561,7 +4542,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>290</v>
       </c>
@@ -4583,7 +4564,6 @@
       <c r="I54" t="s">
         <v>25</v>
       </c>
-      <c r="J54"/>
       <c r="M54" t="s">
         <v>278</v>
       </c>
@@ -4597,7 +4577,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
         <v>293</v>
       </c>
@@ -4622,7 +4602,6 @@
       <c r="I55" t="s">
         <v>25</v>
       </c>
-      <c r="J55"/>
       <c r="M55" t="s">
         <v>278</v>
       </c>
@@ -4636,7 +4615,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>298</v>
       </c>
@@ -4661,7 +4640,6 @@
       <c r="I56" t="s">
         <v>25</v>
       </c>
-      <c r="J56"/>
       <c r="M56" t="s">
         <v>278</v>
       </c>
@@ -4675,7 +4653,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
         <v>304</v>
       </c>
@@ -4700,7 +4678,6 @@
       <c r="I57" t="s">
         <v>25</v>
       </c>
-      <c r="J57"/>
       <c r="M57" t="s">
         <v>307</v>
       </c>
@@ -4714,7 +4691,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
         <v>304</v>
       </c>
@@ -4736,7 +4713,6 @@
       <c r="I58" t="s">
         <v>25</v>
       </c>
-      <c r="J58"/>
       <c r="M58" t="s">
         <v>307</v>
       </c>
@@ -4750,7 +4726,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>310</v>
       </c>
@@ -4772,7 +4748,6 @@
       <c r="I59" t="s">
         <v>25</v>
       </c>
-      <c r="J59"/>
       <c r="M59" t="s">
         <v>307</v>
       </c>
@@ -4786,7 +4761,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
         <v>310</v>
       </c>
@@ -4808,7 +4783,6 @@
       <c r="I60" t="s">
         <v>25</v>
       </c>
-      <c r="J60"/>
       <c r="M60" t="s">
         <v>307</v>
       </c>
@@ -4822,7 +4796,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
         <v>144</v>
       </c>
@@ -4847,7 +4821,6 @@
       <c r="I61" t="s">
         <v>25</v>
       </c>
-      <c r="J61"/>
       <c r="M61" t="s">
         <v>307</v>
       </c>
@@ -4861,7 +4834,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
         <v>318</v>
       </c>
@@ -4883,7 +4856,6 @@
       <c r="I62" t="s">
         <v>25</v>
       </c>
-      <c r="J62"/>
       <c r="M62" t="s">
         <v>307</v>
       </c>
@@ -4897,7 +4869,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
         <v>318</v>
       </c>
@@ -4919,7 +4891,6 @@
       <c r="I63" t="s">
         <v>25</v>
       </c>
-      <c r="J63"/>
       <c r="M63" t="s">
         <v>307</v>
       </c>
@@ -4933,7 +4904,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
         <v>324</v>
       </c>
@@ -4958,7 +4929,6 @@
       <c r="I64" t="s">
         <v>25</v>
       </c>
-      <c r="J64"/>
       <c r="M64" t="s">
         <v>329</v>
       </c>
@@ -4972,7 +4942,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
         <v>331</v>
       </c>
@@ -4997,7 +4967,6 @@
       <c r="I65" t="s">
         <v>25</v>
       </c>
-      <c r="J65"/>
       <c r="M65" t="s">
         <v>334</v>
       </c>
@@ -5008,7 +4977,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
         <v>336</v>
       </c>
@@ -5033,7 +5002,6 @@
       <c r="I66" t="s">
         <v>25</v>
       </c>
-      <c r="J66"/>
       <c r="M66" t="s">
         <v>334</v>
       </c>
@@ -5047,7 +5015,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
         <v>340</v>
       </c>
@@ -5069,7 +5037,6 @@
       <c r="I67" t="s">
         <v>25</v>
       </c>
-      <c r="J67"/>
       <c r="M67" t="s">
         <v>344</v>
       </c>
@@ -5083,7 +5050,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
         <v>346</v>
       </c>
@@ -5108,7 +5075,6 @@
       <c r="I68" t="s">
         <v>25</v>
       </c>
-      <c r="J68"/>
       <c r="M68" t="s">
         <v>344</v>
       </c>
@@ -5122,7 +5088,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
         <v>352</v>
       </c>
@@ -5144,7 +5110,6 @@
       <c r="I69" t="s">
         <v>25</v>
       </c>
-      <c r="J69"/>
       <c r="M69" t="s">
         <v>354</v>
       </c>
@@ -5158,7 +5123,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
         <v>222</v>
       </c>
@@ -5183,7 +5148,6 @@
       <c r="I70" t="s">
         <v>25</v>
       </c>
-      <c r="J70"/>
       <c r="M70" t="s">
         <v>354</v>
       </c>
@@ -5197,7 +5161,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
         <v>357</v>
       </c>
@@ -5222,7 +5186,6 @@
       <c r="I71" t="s">
         <v>25</v>
       </c>
-      <c r="J71"/>
       <c r="M71" t="s">
         <v>362</v>
       </c>
@@ -5236,7 +5199,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="72" spans="1:20">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
         <v>364</v>
       </c>
@@ -5258,7 +5221,6 @@
       <c r="I72" t="s">
         <v>25</v>
       </c>
-      <c r="J72"/>
       <c r="M72" t="s">
         <v>369</v>
       </c>
@@ -5272,7 +5234,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
         <v>371</v>
       </c>
@@ -5297,7 +5259,6 @@
       <c r="I73" t="s">
         <v>25</v>
       </c>
-      <c r="J73"/>
       <c r="M73" t="s">
         <v>374</v>
       </c>
@@ -5311,7 +5272,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
         <v>376</v>
       </c>
@@ -5336,7 +5297,6 @@
       <c r="I74" t="s">
         <v>25</v>
       </c>
-      <c r="J74"/>
       <c r="M74" t="s">
         <v>374</v>
       </c>
@@ -5350,7 +5310,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
         <v>380</v>
       </c>
@@ -5372,7 +5332,6 @@
       <c r="I75" t="s">
         <v>25</v>
       </c>
-      <c r="J75"/>
       <c r="M75" t="s">
         <v>374</v>
       </c>
@@ -5386,7 +5345,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
         <v>383</v>
       </c>
@@ -5411,7 +5370,6 @@
       <c r="I76" t="s">
         <v>25</v>
       </c>
-      <c r="J76"/>
       <c r="M76" t="s">
         <v>374</v>
       </c>
@@ -5425,7 +5383,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
         <v>387</v>
       </c>
@@ -5447,7 +5405,6 @@
       <c r="I77" t="s">
         <v>25</v>
       </c>
-      <c r="J77"/>
       <c r="M77" t="s">
         <v>391</v>
       </c>
@@ -5461,7 +5418,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
         <v>393</v>
       </c>
@@ -5483,7 +5440,6 @@
       <c r="I78" t="s">
         <v>25</v>
       </c>
-      <c r="J78"/>
       <c r="M78" t="s">
         <v>391</v>
       </c>
@@ -5497,7 +5453,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
         <v>397</v>
       </c>
@@ -5519,7 +5475,6 @@
       <c r="I79" t="s">
         <v>25</v>
       </c>
-      <c r="J79"/>
       <c r="M79" t="s">
         <v>399</v>
       </c>
@@ -5533,7 +5488,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
         <v>401</v>
       </c>
@@ -5555,7 +5510,6 @@
       <c r="I80" t="s">
         <v>25</v>
       </c>
-      <c r="J80"/>
       <c r="M80" t="s">
         <v>399</v>
       </c>
@@ -5569,7 +5523,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
         <v>406</v>
       </c>
@@ -5594,7 +5548,6 @@
       <c r="I81" t="s">
         <v>25</v>
       </c>
-      <c r="J81"/>
       <c r="M81" t="s">
         <v>399</v>
       </c>
@@ -5608,7 +5561,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
         <v>411</v>
       </c>
@@ -5630,7 +5583,6 @@
       <c r="I82" t="s">
         <v>25</v>
       </c>
-      <c r="J82"/>
       <c r="M82" t="s">
         <v>415</v>
       </c>
@@ -5644,7 +5596,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
         <v>212</v>
       </c>
@@ -5666,7 +5618,6 @@
       <c r="I83" t="s">
         <v>25</v>
       </c>
-      <c r="J83"/>
       <c r="M83" t="s">
         <v>417</v>
       </c>
@@ -5680,7 +5631,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
         <v>419</v>
       </c>
@@ -5705,7 +5656,6 @@
       <c r="I84" t="s">
         <v>25</v>
       </c>
-      <c r="J84"/>
       <c r="M84" t="s">
         <v>424</v>
       </c>
@@ -5719,7 +5669,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
         <v>426</v>
       </c>
@@ -5741,7 +5691,6 @@
       <c r="I85" t="s">
         <v>25</v>
       </c>
-      <c r="J85"/>
       <c r="M85" t="s">
         <v>430</v>
       </c>
@@ -5755,7 +5704,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="86" spans="1:20">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
         <v>432</v>
       </c>
@@ -5780,7 +5729,6 @@
       <c r="I86" t="s">
         <v>25</v>
       </c>
-      <c r="J86"/>
       <c r="M86" t="s">
         <v>430</v>
       </c>
@@ -5794,7 +5742,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="87" spans="1:20">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
         <v>438</v>
       </c>
@@ -5819,7 +5767,6 @@
       <c r="I87" t="s">
         <v>25</v>
       </c>
-      <c r="J87"/>
       <c r="M87" t="s">
         <v>430</v>
       </c>
@@ -5833,7 +5780,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
         <v>444</v>
       </c>
@@ -5855,7 +5802,6 @@
       <c r="I88" t="s">
         <v>25</v>
       </c>
-      <c r="J88"/>
       <c r="M88" t="s">
         <v>430</v>
       </c>
@@ -5869,7 +5815,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="89" spans="1:20">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
         <v>447</v>
       </c>
@@ -5891,7 +5837,6 @@
       <c r="I89" t="s">
         <v>25</v>
       </c>
-      <c r="J89"/>
       <c r="M89" t="s">
         <v>430</v>
       </c>
@@ -5905,7 +5850,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="1:20">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
         <v>450</v>
       </c>
@@ -5927,7 +5872,6 @@
       <c r="I90" t="s">
         <v>25</v>
       </c>
-      <c r="J90"/>
       <c r="M90" t="s">
         <v>430</v>
       </c>
@@ -5941,7 +5885,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:20">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
         <v>454</v>
       </c>
@@ -5963,7 +5907,6 @@
       <c r="I91" t="s">
         <v>25</v>
       </c>
-      <c r="J91"/>
       <c r="M91" t="s">
         <v>430</v>
       </c>
@@ -5977,7 +5920,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
         <v>411</v>
       </c>
@@ -5999,7 +5942,6 @@
       <c r="I92" t="s">
         <v>25</v>
       </c>
-      <c r="J92"/>
       <c r="M92" t="s">
         <v>430</v>
       </c>
@@ -6013,7 +5955,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
         <v>460</v>
       </c>
@@ -6038,7 +5980,6 @@
       <c r="I93" t="s">
         <v>25</v>
       </c>
-      <c r="J93"/>
       <c r="M93" t="s">
         <v>430</v>
       </c>
@@ -6052,7 +5993,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="94" spans="1:20">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="3">
         <v>6067204</v>
       </c>
@@ -6077,7 +6018,6 @@
       <c r="I94" t="s">
         <v>25</v>
       </c>
-      <c r="J94"/>
       <c r="M94" t="s">
         <v>131</v>
       </c>
@@ -6088,7 +6028,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="95" spans="1:20">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
         <v>468</v>
       </c>
@@ -6113,7 +6053,6 @@
       <c r="I95" t="s">
         <v>25</v>
       </c>
-      <c r="J95"/>
       <c r="M95" t="s">
         <v>278</v>
       </c>
@@ -6127,7 +6066,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="96" spans="1:20">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
         <v>474</v>
       </c>
@@ -6152,7 +6091,6 @@
       <c r="I96" t="s">
         <v>25</v>
       </c>
-      <c r="J96"/>
       <c r="M96" t="s">
         <v>307</v>
       </c>
@@ -6163,7 +6101,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
         <v>480</v>
       </c>
@@ -6188,7 +6126,6 @@
       <c r="I97" t="s">
         <v>25</v>
       </c>
-      <c r="J97"/>
       <c r="M97" t="s">
         <v>307</v>
       </c>
@@ -6199,7 +6136,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="98" spans="1:20">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
         <v>249</v>
       </c>
@@ -6224,7 +6161,6 @@
       <c r="I98" t="s">
         <v>25</v>
       </c>
-      <c r="J98"/>
       <c r="M98" t="s">
         <v>307</v>
       </c>
@@ -6238,7 +6174,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B99" s="3" t="s">
         <v>485</v>
       </c>
@@ -6263,21 +6199,20 @@
       <c r="I99" t="s">
         <v>25</v>
       </c>
-      <c r="J99"/>
       <c r="M99" t="s">
         <v>307</v>
       </c>
       <c r="N99" t="s">
         <v>490</v>
       </c>
-      <c r="O99" s="4" t="s">
+      <c r="O99" t="s">
         <v>491</v>
       </c>
       <c r="P99" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B100" s="3" t="s">
         <v>492</v>
       </c>
@@ -6302,7 +6237,6 @@
       <c r="I100" t="s">
         <v>25</v>
       </c>
-      <c r="J100"/>
       <c r="M100" t="s">
         <v>334</v>
       </c>
@@ -6316,7 +6250,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B101" s="3" t="s">
         <v>496</v>
       </c>
@@ -6341,7 +6275,6 @@
       <c r="I101" t="s">
         <v>25</v>
       </c>
-      <c r="J101"/>
       <c r="M101" t="s">
         <v>362</v>
       </c>
@@ -6355,7 +6288,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="102" spans="1:20">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B102" s="3" t="s">
         <v>502</v>
       </c>
@@ -6380,7 +6313,6 @@
       <c r="I102" t="s">
         <v>25</v>
       </c>
-      <c r="J102"/>
       <c r="M102" t="s">
         <v>362</v>
       </c>
@@ -6391,7 +6323,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
         <v>508</v>
       </c>
@@ -6416,7 +6348,6 @@
       <c r="I103" t="s">
         <v>25</v>
       </c>
-      <c r="J103"/>
       <c r="M103" t="s">
         <v>369</v>
       </c>
@@ -6430,7 +6361,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B104" s="3" t="s">
         <v>438</v>
       </c>
@@ -6455,7 +6386,6 @@
       <c r="I104" t="s">
         <v>25</v>
       </c>
-      <c r="J104"/>
       <c r="M104" t="s">
         <v>374</v>
       </c>
@@ -6466,7 +6396,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B105" s="3" t="s">
         <v>444</v>
       </c>
@@ -6488,7 +6418,6 @@
       <c r="I105" t="s">
         <v>25</v>
       </c>
-      <c r="J105"/>
       <c r="M105" t="s">
         <v>374</v>
       </c>
@@ -6502,7 +6431,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B106" s="3" t="s">
         <v>447</v>
       </c>
@@ -6524,7 +6453,6 @@
       <c r="I106" t="s">
         <v>25</v>
       </c>
-      <c r="J106"/>
       <c r="M106" t="s">
         <v>374</v>
       </c>
@@ -6538,7 +6466,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B107" s="3" t="s">
         <v>450</v>
       </c>
@@ -6560,7 +6488,6 @@
       <c r="I107" t="s">
         <v>25</v>
       </c>
-      <c r="J107"/>
       <c r="M107" t="s">
         <v>374</v>
       </c>
@@ -6574,7 +6501,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="108" spans="1:20">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B108" s="3" t="s">
         <v>519</v>
       </c>
@@ -6599,7 +6526,6 @@
       <c r="I108" t="s">
         <v>25</v>
       </c>
-      <c r="J108"/>
       <c r="M108" t="s">
         <v>374</v>
       </c>
@@ -6613,7 +6539,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B109" s="3" t="s">
         <v>523</v>
       </c>
@@ -6638,7 +6564,6 @@
       <c r="I109" t="s">
         <v>25</v>
       </c>
-      <c r="J109"/>
       <c r="M109" t="s">
         <v>374</v>
       </c>
@@ -6652,7 +6577,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B110" s="3" t="s">
         <v>527</v>
       </c>
@@ -6677,7 +6602,6 @@
       <c r="I110" t="s">
         <v>25</v>
       </c>
-      <c r="J110"/>
       <c r="M110" t="s">
         <v>374</v>
       </c>
@@ -6691,7 +6615,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="111" spans="1:20">
+    <row r="111" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B111" s="3" t="s">
         <v>532</v>
       </c>
@@ -6716,7 +6640,6 @@
       <c r="I111" t="s">
         <v>25</v>
       </c>
-      <c r="J111"/>
       <c r="M111" t="s">
         <v>391</v>
       </c>
@@ -6730,7 +6653,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B112" s="3" t="s">
         <v>536</v>
       </c>
@@ -6755,7 +6678,6 @@
       <c r="I112" t="s">
         <v>25</v>
       </c>
-      <c r="J112"/>
       <c r="M112" t="s">
         <v>391</v>
       </c>
@@ -6769,7 +6691,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="113" spans="1:20">
+    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B113" s="3" t="s">
         <v>540</v>
       </c>
@@ -6794,7 +6716,6 @@
       <c r="I113" t="s">
         <v>25</v>
       </c>
-      <c r="J113"/>
       <c r="M113" t="s">
         <v>543</v>
       </c>
@@ -6805,7 +6726,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="114" spans="1:20">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B114" s="3" t="s">
         <v>468</v>
       </c>
@@ -6830,7 +6751,6 @@
       <c r="I114" t="s">
         <v>25</v>
       </c>
-      <c r="J114"/>
       <c r="M114" t="s">
         <v>543</v>
       </c>
@@ -6841,7 +6761,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="115" spans="1:20">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B115" s="3" t="s">
         <v>546</v>
       </c>
@@ -6866,7 +6786,6 @@
       <c r="I115" t="s">
         <v>25</v>
       </c>
-      <c r="J115"/>
       <c r="M115" t="s">
         <v>551</v>
       </c>
@@ -6877,7 +6796,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="116" spans="1:20">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B116" s="3">
         <v>415016301</v>
       </c>
@@ -6899,7 +6818,6 @@
       <c r="I116" t="s">
         <v>556</v>
       </c>
-      <c r="J116"/>
       <c r="O116" t="s">
         <v>557</v>
       </c>
@@ -6907,7 +6825,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="117" spans="1:20">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B117" s="3">
         <v>324108103</v>
       </c>
@@ -6929,7 +6847,6 @@
       <c r="I117" t="s">
         <v>25</v>
       </c>
-      <c r="J117"/>
       <c r="O117" t="s">
         <v>557</v>
       </c>
@@ -6937,7 +6854,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B118" s="3">
         <v>406039002</v>
       </c>
@@ -6959,7 +6876,6 @@
       <c r="I118" t="s">
         <v>562</v>
       </c>
-      <c r="J118"/>
       <c r="O118" t="s">
         <v>557</v>
       </c>
@@ -6967,7 +6883,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B119" s="3">
         <v>409047703</v>
       </c>
@@ -6989,7 +6905,6 @@
       <c r="I119" t="s">
         <v>564</v>
       </c>
-      <c r="J119"/>
       <c r="O119" t="s">
         <v>557</v>
       </c>
@@ -6997,7 +6912,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="120" spans="1:20">
+    <row r="120" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B120" s="3">
         <v>427057407</v>
       </c>
@@ -7019,7 +6934,6 @@
       <c r="I120" t="s">
         <v>567</v>
       </c>
-      <c r="J120"/>
       <c r="O120" t="s">
         <v>557</v>
       </c>
@@ -7027,7 +6941,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="121" spans="1:20">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B121" s="3">
         <v>428038302</v>
       </c>
@@ -7049,7 +6963,6 @@
       <c r="I121" t="s">
         <v>570</v>
       </c>
-      <c r="J121"/>
       <c r="O121" t="s">
         <v>557</v>
       </c>
@@ -7057,7 +6970,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="122" spans="1:20">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B122" s="3">
         <v>406068904</v>
       </c>
@@ -7079,7 +6992,6 @@
       <c r="I122" t="s">
         <v>562</v>
       </c>
-      <c r="J122"/>
       <c r="O122" t="s">
         <v>557</v>
       </c>
@@ -7087,7 +6999,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="123" spans="1:20">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B123" s="3">
         <v>2104066201</v>
       </c>
@@ -7119,7 +7031,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B124" s="3">
         <v>307069501</v>
       </c>
@@ -7151,7 +7063,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="125" spans="1:20">
+    <row r="125" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B125" s="3">
         <v>416098301</v>
       </c>
@@ -7173,7 +7085,6 @@
       <c r="I125" t="s">
         <v>580</v>
       </c>
-      <c r="J125"/>
       <c r="O125" t="s">
         <v>557</v>
       </c>
@@ -7181,7 +7092,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="126" spans="1:20">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B126" s="3">
         <v>109118101</v>
       </c>
@@ -7213,7 +7124,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="127" spans="1:20">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B127" s="3">
         <v>607079301</v>
       </c>
@@ -7235,7 +7146,6 @@
       <c r="I127" t="s">
         <v>583</v>
       </c>
-      <c r="J127"/>
       <c r="O127" t="s">
         <v>557</v>
       </c>
@@ -7243,7 +7153,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="128" spans="1:20">
+    <row r="128" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B128" s="3">
         <v>428118601</v>
       </c>
@@ -7275,7 +7185,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="129" spans="1:20">
+    <row r="129" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B129" s="3">
         <v>402019003</v>
       </c>
@@ -7297,7 +7207,6 @@
       <c r="I129" t="s">
         <v>562</v>
       </c>
-      <c r="J129"/>
       <c r="O129" t="s">
         <v>557</v>
       </c>
@@ -7305,7 +7214,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="130" spans="1:20">
+    <row r="130" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B130" s="3">
         <v>416069101</v>
       </c>
@@ -7327,7 +7236,6 @@
       <c r="I130" t="s">
         <v>570</v>
       </c>
-      <c r="J130"/>
       <c r="O130" t="s">
         <v>557</v>
       </c>
@@ -7335,7 +7243,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="131" spans="1:20">
+    <row r="131" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B131" s="3">
         <v>429018903</v>
       </c>
@@ -7357,7 +7265,6 @@
       <c r="I131" t="s">
         <v>570</v>
       </c>
-      <c r="J131"/>
       <c r="O131" t="s">
         <v>557</v>
       </c>
@@ -7365,7 +7272,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="132" spans="1:20">
+    <row r="132" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B132" s="3">
         <v>313126401</v>
       </c>
@@ -7397,7 +7304,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="133" spans="1:20">
+    <row r="133" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B133" s="3">
         <v>320046101</v>
       </c>
@@ -7419,7 +7326,6 @@
       <c r="I133" t="s">
         <v>570</v>
       </c>
-      <c r="J133"/>
       <c r="O133" t="s">
         <v>557</v>
       </c>
@@ -7427,7 +7333,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="134" spans="1:20">
+    <row r="134" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B134" s="3">
         <v>418078701</v>
       </c>
@@ -7459,7 +7365,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="135" spans="1:20">
+    <row r="135" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B135" s="3">
         <v>603038002</v>
       </c>
@@ -7481,7 +7387,6 @@
       <c r="I135" t="s">
         <v>580</v>
       </c>
-      <c r="J135"/>
       <c r="O135" t="s">
         <v>557</v>
       </c>
@@ -7489,7 +7394,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="136" spans="1:20">
+    <row r="136" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B136" s="3">
         <v>415039101</v>
       </c>
@@ -7511,7 +7416,6 @@
       <c r="I136" t="s">
         <v>580</v>
       </c>
-      <c r="J136"/>
       <c r="O136" t="s">
         <v>557</v>
       </c>
@@ -7519,7 +7423,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="137" spans="1:20">
+    <row r="137" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B137" s="3">
         <v>401117901</v>
       </c>
@@ -7541,7 +7445,6 @@
       <c r="I137" t="s">
         <v>25</v>
       </c>
-      <c r="J137"/>
       <c r="O137" t="s">
         <v>557</v>
       </c>
@@ -7549,7 +7452,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="138" spans="1:20">
+    <row r="138" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B138" s="3">
         <v>419078903</v>
       </c>
@@ -7571,7 +7474,6 @@
       <c r="I138" t="s">
         <v>25</v>
       </c>
-      <c r="J138"/>
       <c r="O138" t="s">
         <v>557</v>
       </c>
@@ -7579,7 +7481,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="139" spans="1:20">
+    <row r="139" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B139" s="3">
         <v>430119102</v>
       </c>
@@ -7601,7 +7503,6 @@
       <c r="I139" t="s">
         <v>580</v>
       </c>
-      <c r="J139"/>
       <c r="O139" t="s">
         <v>557</v>
       </c>
@@ -7609,7 +7510,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="140" spans="1:20">
+    <row r="140" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B140" s="3">
         <v>428078803</v>
       </c>
@@ -7631,7 +7532,6 @@
       <c r="I140" t="s">
         <v>562</v>
       </c>
-      <c r="J140"/>
       <c r="O140" t="s">
         <v>557</v>
       </c>
@@ -7639,7 +7539,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="141" spans="1:20">
+    <row r="141" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B141" s="3">
         <v>628118902</v>
       </c>
@@ -7661,7 +7561,6 @@
       <c r="I141" t="s">
         <v>580</v>
       </c>
-      <c r="J141"/>
       <c r="O141" t="s">
         <v>557</v>
       </c>
@@ -7669,7 +7568,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="142" spans="1:20">
+    <row r="142" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B142" s="3">
         <v>420088503</v>
       </c>
@@ -7701,7 +7600,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="143" spans="1:20">
+    <row r="143" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B143" s="3">
         <v>428118904</v>
       </c>
@@ -7723,7 +7622,6 @@
       <c r="I143" t="s">
         <v>570</v>
       </c>
-      <c r="J143"/>
       <c r="O143" t="s">
         <v>557</v>
       </c>
@@ -7731,7 +7629,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="144" spans="1:20">
+    <row r="144" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B144" s="3">
         <v>415028303</v>
       </c>
@@ -7753,7 +7651,6 @@
       <c r="I144" t="s">
         <v>603</v>
       </c>
-      <c r="J144"/>
       <c r="O144" t="s">
         <v>557</v>
       </c>
@@ -7761,7 +7658,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="145" spans="1:20">
+    <row r="145" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B145" s="3">
         <v>2928037201</v>
       </c>
@@ -7793,7 +7690,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="146" spans="1:20">
+    <row r="146" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B146" s="3">
         <v>420087402</v>
       </c>
@@ -7815,7 +7712,6 @@
       <c r="I146" t="s">
         <v>570</v>
       </c>
-      <c r="J146"/>
       <c r="O146" t="s">
         <v>557</v>
       </c>
@@ -7823,7 +7719,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="147" spans="1:20">
+    <row r="147" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B147" s="3">
         <v>306046502</v>
       </c>
@@ -7845,7 +7741,6 @@
       <c r="I147" t="s">
         <v>25</v>
       </c>
-      <c r="J147"/>
       <c r="O147" t="s">
         <v>557</v>
       </c>
@@ -7853,7 +7748,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="148" spans="1:20">
+    <row r="148" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B148" s="3">
         <v>430079201</v>
       </c>
@@ -7875,7 +7770,6 @@
       <c r="I148" t="s">
         <v>564</v>
       </c>
-      <c r="J148"/>
       <c r="O148" t="s">
         <v>557</v>
       </c>
@@ -7883,7 +7777,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="149" spans="1:20">
+    <row r="149" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B149" s="3">
         <v>430068301</v>
       </c>
@@ -7905,7 +7799,6 @@
       <c r="I149" t="s">
         <v>562</v>
       </c>
-      <c r="J149"/>
       <c r="O149" t="s">
         <v>557</v>
       </c>
@@ -7913,7 +7806,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="150" spans="1:20">
+    <row r="150" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B150" s="3">
         <v>415016301</v>
       </c>
@@ -7935,7 +7828,6 @@
       <c r="I150" t="s">
         <v>556</v>
       </c>
-      <c r="J150"/>
       <c r="O150" t="s">
         <v>610</v>
       </c>
@@ -7943,7 +7835,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="151" spans="1:20">
+    <row r="151" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B151" s="3">
         <v>324108103</v>
       </c>
@@ -7965,7 +7857,6 @@
       <c r="I151" t="s">
         <v>25</v>
       </c>
-      <c r="J151"/>
       <c r="O151" t="s">
         <v>610</v>
       </c>
@@ -7973,7 +7864,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="152" spans="1:20">
+    <row r="152" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B152" s="3">
         <v>406039002</v>
       </c>
@@ -7995,7 +7886,6 @@
       <c r="I152" t="s">
         <v>562</v>
       </c>
-      <c r="J152"/>
       <c r="O152" t="s">
         <v>610</v>
       </c>
@@ -8003,7 +7893,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="153" spans="1:20">
+    <row r="153" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B153" s="3">
         <v>409047703</v>
       </c>
@@ -8025,7 +7915,6 @@
       <c r="I153" t="s">
         <v>564</v>
       </c>
-      <c r="J153"/>
       <c r="O153" t="s">
         <v>610</v>
       </c>
@@ -8033,7 +7922,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="154" spans="1:20">
+    <row r="154" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B154" s="3">
         <v>427057407</v>
       </c>
@@ -8055,7 +7944,6 @@
       <c r="I154" t="s">
         <v>567</v>
       </c>
-      <c r="J154"/>
       <c r="O154" t="s">
         <v>610</v>
       </c>
@@ -8063,7 +7951,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="155" spans="1:20">
+    <row r="155" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B155" s="3">
         <v>428038302</v>
       </c>
@@ -8085,7 +7973,6 @@
       <c r="I155" t="s">
         <v>570</v>
       </c>
-      <c r="J155"/>
       <c r="O155" t="s">
         <v>610</v>
       </c>
@@ -8093,7 +7980,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="156" spans="1:20">
+    <row r="156" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B156" s="3">
         <v>406068904</v>
       </c>
@@ -8115,7 +8002,6 @@
       <c r="I156" t="s">
         <v>562</v>
       </c>
-      <c r="J156"/>
       <c r="O156" t="s">
         <v>610</v>
       </c>
@@ -8123,7 +8009,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="157" spans="1:20">
+    <row r="157" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B157" s="3">
         <v>2104066201</v>
       </c>
@@ -8155,7 +8041,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="158" spans="1:20">
+    <row r="158" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B158" s="3">
         <v>307069501</v>
       </c>
@@ -8187,7 +8073,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="159" spans="1:20">
+    <row r="159" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B159" s="3">
         <v>416098301</v>
       </c>
@@ -8209,7 +8095,6 @@
       <c r="I159" t="s">
         <v>580</v>
       </c>
-      <c r="J159"/>
       <c r="O159" t="s">
         <v>610</v>
       </c>
@@ -8217,7 +8102,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="160" spans="1:20">
+    <row r="160" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B160" s="3">
         <v>109118101</v>
       </c>
@@ -8249,7 +8134,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="161" spans="1:20">
+    <row r="161" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B161" s="3">
         <v>607079301</v>
       </c>
@@ -8271,7 +8156,6 @@
       <c r="I161" t="s">
         <v>583</v>
       </c>
-      <c r="J161"/>
       <c r="O161" t="s">
         <v>610</v>
       </c>
@@ -8279,7 +8163,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="162" spans="1:20">
+    <row r="162" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B162" s="3">
         <v>428118601</v>
       </c>
@@ -8311,7 +8195,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="163" spans="1:20">
+    <row r="163" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B163" s="3">
         <v>402019003</v>
       </c>
@@ -8333,7 +8217,6 @@
       <c r="I163" t="s">
         <v>562</v>
       </c>
-      <c r="J163"/>
       <c r="O163" t="s">
         <v>610</v>
       </c>
@@ -8341,7 +8224,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="164" spans="1:20">
+    <row r="164" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B164" s="3">
         <v>416069101</v>
       </c>
@@ -8363,7 +8246,6 @@
       <c r="I164" t="s">
         <v>570</v>
       </c>
-      <c r="J164"/>
       <c r="O164" t="s">
         <v>610</v>
       </c>
@@ -8371,7 +8253,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B165" s="3">
         <v>429018903</v>
       </c>
@@ -8393,7 +8275,6 @@
       <c r="I165" t="s">
         <v>570</v>
       </c>
-      <c r="J165"/>
       <c r="O165" t="s">
         <v>610</v>
       </c>
@@ -8401,7 +8282,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B166" s="3">
         <v>313126401</v>
       </c>
@@ -8433,7 +8314,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B167" s="3">
         <v>320046101</v>
       </c>
@@ -8455,7 +8336,6 @@
       <c r="I167" t="s">
         <v>570</v>
       </c>
-      <c r="J167"/>
       <c r="O167" t="s">
         <v>610</v>
       </c>
@@ -8463,7 +8343,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B168" s="3">
         <v>418078701</v>
       </c>
@@ -8495,7 +8375,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B169" s="3">
         <v>603038002</v>
       </c>
@@ -8517,7 +8397,6 @@
       <c r="I169" t="s">
         <v>580</v>
       </c>
-      <c r="J169"/>
       <c r="O169" t="s">
         <v>610</v>
       </c>
@@ -8525,7 +8404,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="170" spans="1:20">
+    <row r="170" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B170" s="3">
         <v>415039101</v>
       </c>
@@ -8547,7 +8426,6 @@
       <c r="I170" t="s">
         <v>580</v>
       </c>
-      <c r="J170"/>
       <c r="O170" t="s">
         <v>610</v>
       </c>
@@ -8555,7 +8433,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B171" s="3">
         <v>401117901</v>
       </c>
@@ -8577,7 +8455,6 @@
       <c r="I171" t="s">
         <v>25</v>
       </c>
-      <c r="J171"/>
       <c r="O171" t="s">
         <v>610</v>
       </c>
@@ -8585,7 +8462,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="172" spans="1:20">
+    <row r="172" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B172" s="3">
         <v>419078903</v>
       </c>
@@ -8607,7 +8484,6 @@
       <c r="I172" t="s">
         <v>25</v>
       </c>
-      <c r="J172"/>
       <c r="O172" t="s">
         <v>610</v>
       </c>
@@ -8615,7 +8491,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="173" spans="1:20">
+    <row r="173" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B173" s="3">
         <v>430119102</v>
       </c>
@@ -8637,7 +8513,6 @@
       <c r="I173" t="s">
         <v>580</v>
       </c>
-      <c r="J173"/>
       <c r="O173" t="s">
         <v>610</v>
       </c>
@@ -8645,7 +8520,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B174" s="3">
         <v>428078803</v>
       </c>
@@ -8667,7 +8542,6 @@
       <c r="I174" t="s">
         <v>562</v>
       </c>
-      <c r="J174"/>
       <c r="O174" t="s">
         <v>610</v>
       </c>
@@ -8675,7 +8549,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="175" spans="1:20">
+    <row r="175" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B175" s="3">
         <v>628118902</v>
       </c>
@@ -8697,7 +8571,6 @@
       <c r="I175" t="s">
         <v>580</v>
       </c>
-      <c r="J175"/>
       <c r="O175" t="s">
         <v>610</v>
       </c>
@@ -8705,7 +8578,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="176" spans="1:20">
+    <row r="176" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B176" s="3">
         <v>420088503</v>
       </c>
@@ -8737,7 +8610,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="177" spans="1:20">
+    <row r="177" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B177" s="3">
         <v>428118904</v>
       </c>
@@ -8759,7 +8632,6 @@
       <c r="I177" t="s">
         <v>570</v>
       </c>
-      <c r="J177"/>
       <c r="O177" t="s">
         <v>610</v>
       </c>
@@ -8767,7 +8639,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="178" spans="1:20">
+    <row r="178" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B178" s="3">
         <v>415028303</v>
       </c>
@@ -8789,7 +8661,6 @@
       <c r="I178" t="s">
         <v>603</v>
       </c>
-      <c r="J178"/>
       <c r="O178" t="s">
         <v>610</v>
       </c>
@@ -8797,7 +8668,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="179" spans="1:20">
+    <row r="179" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B179" s="3">
         <v>2928037201</v>
       </c>
@@ -8829,7 +8700,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="180" spans="1:20">
+    <row r="180" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B180" s="3">
         <v>420087402</v>
       </c>
@@ -8851,7 +8722,6 @@
       <c r="I180" t="s">
         <v>570</v>
       </c>
-      <c r="J180"/>
       <c r="O180" t="s">
         <v>610</v>
       </c>
@@ -8859,7 +8729,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="181" spans="1:20">
+    <row r="181" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B181" s="3">
         <v>306046502</v>
       </c>
@@ -8881,7 +8751,6 @@
       <c r="I181" t="s">
         <v>25</v>
       </c>
-      <c r="J181"/>
       <c r="O181" t="s">
         <v>610</v>
       </c>
@@ -8889,7 +8758,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="182" spans="1:20">
+    <row r="182" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B182" s="3">
         <v>430079201</v>
       </c>
@@ -8911,7 +8780,6 @@
       <c r="I182" t="s">
         <v>564</v>
       </c>
-      <c r="J182"/>
       <c r="O182" t="s">
         <v>610</v>
       </c>
@@ -8919,7 +8787,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="183" spans="1:20">
+    <row r="183" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B183" s="3">
         <v>430068301</v>
       </c>
@@ -8941,7 +8809,6 @@
       <c r="I183" t="s">
         <v>562</v>
       </c>
-      <c r="J183"/>
       <c r="O183" t="s">
         <v>610</v>
       </c>
@@ -8949,7 +8816,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="184" spans="1:20">
+    <row r="184" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B184" s="3">
         <v>415016301</v>
       </c>
@@ -8971,7 +8838,6 @@
       <c r="I184" t="s">
         <v>556</v>
       </c>
-      <c r="J184"/>
       <c r="O184" t="s">
         <v>611</v>
       </c>
@@ -8979,7 +8845,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="185" spans="1:20">
+    <row r="185" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B185" s="3">
         <v>324108103</v>
       </c>
@@ -9001,7 +8867,6 @@
       <c r="I185" t="s">
         <v>25</v>
       </c>
-      <c r="J185"/>
       <c r="O185" t="s">
         <v>611</v>
       </c>
@@ -9009,7 +8874,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="186" spans="1:20">
+    <row r="186" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B186" s="3">
         <v>406039002</v>
       </c>
@@ -9031,7 +8896,6 @@
       <c r="I186" t="s">
         <v>562</v>
       </c>
-      <c r="J186"/>
       <c r="O186" t="s">
         <v>611</v>
       </c>
@@ -9039,7 +8903,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="187" spans="1:20">
+    <row r="187" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B187" s="3">
         <v>409047703</v>
       </c>
@@ -9061,7 +8925,6 @@
       <c r="I187" t="s">
         <v>564</v>
       </c>
-      <c r="J187"/>
       <c r="O187" t="s">
         <v>611</v>
       </c>
@@ -9069,7 +8932,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="188" spans="1:20">
+    <row r="188" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B188" s="3">
         <v>427057407</v>
       </c>
@@ -9091,7 +8954,6 @@
       <c r="I188" t="s">
         <v>567</v>
       </c>
-      <c r="J188"/>
       <c r="O188" t="s">
         <v>611</v>
       </c>
@@ -9099,7 +8961,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="189" spans="1:20">
+    <row r="189" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B189" s="3">
         <v>428038302</v>
       </c>
@@ -9121,7 +8983,6 @@
       <c r="I189" t="s">
         <v>570</v>
       </c>
-      <c r="J189"/>
       <c r="O189" t="s">
         <v>611</v>
       </c>
@@ -9129,7 +8990,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B190" s="3">
         <v>406068904</v>
       </c>
@@ -9151,7 +9012,6 @@
       <c r="I190" t="s">
         <v>562</v>
       </c>
-      <c r="J190"/>
       <c r="O190" t="s">
         <v>611</v>
       </c>
@@ -9159,7 +9019,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B191" s="3">
         <v>2104066201</v>
       </c>
@@ -9191,7 +9051,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B192" s="3">
         <v>307069501</v>
       </c>
@@ -9223,7 +9083,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B193" s="3">
         <v>416098301</v>
       </c>
@@ -9245,7 +9105,6 @@
       <c r="I193" t="s">
         <v>580</v>
       </c>
-      <c r="J193"/>
       <c r="O193" t="s">
         <v>611</v>
       </c>
@@ -9253,7 +9112,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B194" s="3">
         <v>109118101</v>
       </c>
@@ -9285,7 +9144,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B195" s="3">
         <v>607079301</v>
       </c>
@@ -9307,7 +9166,6 @@
       <c r="I195" t="s">
         <v>583</v>
       </c>
-      <c r="J195"/>
       <c r="O195" t="s">
         <v>611</v>
       </c>
@@ -9315,7 +9173,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B196" s="3">
         <v>428118601</v>
       </c>
@@ -9347,7 +9205,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B197" s="3">
         <v>402019003</v>
       </c>
@@ -9369,7 +9227,6 @@
       <c r="I197" t="s">
         <v>562</v>
       </c>
-      <c r="J197"/>
       <c r="O197" t="s">
         <v>611</v>
       </c>
@@ -9377,7 +9234,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B198" s="3">
         <v>416069101</v>
       </c>
@@ -9399,7 +9256,6 @@
       <c r="I198" t="s">
         <v>570</v>
       </c>
-      <c r="J198"/>
       <c r="O198" t="s">
         <v>611</v>
       </c>
@@ -9407,7 +9263,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B199" s="3">
         <v>429018903</v>
       </c>
@@ -9429,7 +9285,6 @@
       <c r="I199" t="s">
         <v>570</v>
       </c>
-      <c r="J199"/>
       <c r="O199" t="s">
         <v>611</v>
       </c>
@@ -9437,7 +9292,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B200" s="3">
         <v>313126401</v>
       </c>
@@ -9469,7 +9324,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B201" s="3">
         <v>320046101</v>
       </c>
@@ -9491,7 +9346,6 @@
       <c r="I201" t="s">
         <v>570</v>
       </c>
-      <c r="J201"/>
       <c r="O201" t="s">
         <v>611</v>
       </c>
@@ -9499,7 +9353,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B202" s="3">
         <v>418078701</v>
       </c>
@@ -9531,7 +9385,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B203" s="3">
         <v>603038002</v>
       </c>
@@ -9553,7 +9407,6 @@
       <c r="I203" t="s">
         <v>580</v>
       </c>
-      <c r="J203"/>
       <c r="O203" t="s">
         <v>611</v>
       </c>
@@ -9561,7 +9414,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B204" s="3">
         <v>415039101</v>
       </c>
@@ -9583,7 +9436,6 @@
       <c r="I204" t="s">
         <v>580</v>
       </c>
-      <c r="J204"/>
       <c r="O204" t="s">
         <v>611</v>
       </c>
@@ -9591,7 +9443,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B205" s="3">
         <v>401117901</v>
       </c>
@@ -9613,7 +9465,6 @@
       <c r="I205" t="s">
         <v>25</v>
       </c>
-      <c r="J205"/>
       <c r="O205" t="s">
         <v>611</v>
       </c>
@@ -9621,7 +9472,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B206" s="3">
         <v>419078903</v>
       </c>
@@ -9643,7 +9494,6 @@
       <c r="I206" t="s">
         <v>25</v>
       </c>
-      <c r="J206"/>
       <c r="O206" t="s">
         <v>611</v>
       </c>
@@ -9651,7 +9501,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B207" s="3">
         <v>430119102</v>
       </c>
@@ -9673,7 +9523,6 @@
       <c r="I207" t="s">
         <v>580</v>
       </c>
-      <c r="J207"/>
       <c r="O207" t="s">
         <v>611</v>
       </c>
@@ -9681,7 +9530,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B208" s="3">
         <v>428078803</v>
       </c>
@@ -9703,7 +9552,6 @@
       <c r="I208" t="s">
         <v>562</v>
       </c>
-      <c r="J208"/>
       <c r="O208" t="s">
         <v>611</v>
       </c>
@@ -9711,7 +9559,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="209" spans="1:20">
+    <row r="209" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B209" s="3">
         <v>628118902</v>
       </c>
@@ -9733,7 +9581,6 @@
       <c r="I209" t="s">
         <v>580</v>
       </c>
-      <c r="J209"/>
       <c r="O209" t="s">
         <v>611</v>
       </c>
@@ -9741,7 +9588,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="210" spans="1:20">
+    <row r="210" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B210" s="3">
         <v>420088503</v>
       </c>
@@ -9773,7 +9620,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="211" spans="1:20">
+    <row r="211" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B211" s="3">
         <v>428118904</v>
       </c>
@@ -9795,7 +9642,6 @@
       <c r="I211" t="s">
         <v>570</v>
       </c>
-      <c r="J211"/>
       <c r="O211" t="s">
         <v>611</v>
       </c>
@@ -9803,7 +9649,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="212" spans="1:20">
+    <row r="212" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B212" s="3">
         <v>415028303</v>
       </c>
@@ -9825,7 +9671,6 @@
       <c r="I212" t="s">
         <v>603</v>
       </c>
-      <c r="J212"/>
       <c r="O212" t="s">
         <v>611</v>
       </c>
@@ -9833,7 +9678,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="213" spans="1:20">
+    <row r="213" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B213" s="3">
         <v>2928037201</v>
       </c>
@@ -9865,7 +9710,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="214" spans="1:20">
+    <row r="214" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B214" s="3">
         <v>420087402</v>
       </c>
@@ -9887,7 +9732,6 @@
       <c r="I214" t="s">
         <v>570</v>
       </c>
-      <c r="J214"/>
       <c r="O214" t="s">
         <v>611</v>
       </c>
@@ -9895,7 +9739,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="215" spans="1:20">
+    <row r="215" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B215" s="3">
         <v>306046502</v>
       </c>
@@ -9917,7 +9761,6 @@
       <c r="I215" t="s">
         <v>25</v>
       </c>
-      <c r="J215"/>
       <c r="O215" t="s">
         <v>611</v>
       </c>
@@ -9925,7 +9768,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="216" spans="1:20">
+    <row r="216" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B216" s="3">
         <v>430079201</v>
       </c>
@@ -9947,7 +9790,6 @@
       <c r="I216" t="s">
         <v>564</v>
       </c>
-      <c r="J216"/>
       <c r="O216" t="s">
         <v>611</v>
       </c>
@@ -9955,7 +9797,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="217" spans="1:20">
+    <row r="217" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B217" s="3">
         <v>430068301</v>
       </c>
@@ -9977,7 +9819,6 @@
       <c r="I217" t="s">
         <v>562</v>
       </c>
-      <c r="J217"/>
       <c r="O217" t="s">
         <v>611</v>
       </c>
@@ -9985,7 +9826,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="218" spans="1:20">
+    <row r="218" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B218" s="3">
         <v>2104066201</v>
       </c>
@@ -10017,7 +9858,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="219" spans="1:20">
+    <row r="219" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B219" s="3">
         <v>307069501</v>
       </c>
@@ -10049,7 +9890,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="220" spans="1:20">
+    <row r="220" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B220" s="3">
         <v>416098301</v>
       </c>
@@ -10071,7 +9912,6 @@
       <c r="I220" t="s">
         <v>580</v>
       </c>
-      <c r="J220"/>
       <c r="O220" t="s">
         <v>612</v>
       </c>
@@ -10079,7 +9919,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="221" spans="1:20">
+    <row r="221" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B221" s="3">
         <v>109118101</v>
       </c>
@@ -10111,7 +9951,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="222" spans="1:20">
+    <row r="222" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B222" s="3">
         <v>607079301</v>
       </c>
@@ -10133,7 +9973,6 @@
       <c r="I222" t="s">
         <v>583</v>
       </c>
-      <c r="J222"/>
       <c r="O222" t="s">
         <v>612</v>
       </c>
@@ -10141,7 +9980,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="223" spans="1:20">
+    <row r="223" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B223" s="3">
         <v>402019003</v>
       </c>
@@ -10163,7 +10002,6 @@
       <c r="I223" t="s">
         <v>562</v>
       </c>
-      <c r="J223"/>
       <c r="O223" t="s">
         <v>612</v>
       </c>
@@ -10171,7 +10009,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="224" spans="1:20">
+    <row r="224" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B224" s="3">
         <v>416069101</v>
       </c>
@@ -10193,7 +10031,6 @@
       <c r="I224" t="s">
         <v>570</v>
       </c>
-      <c r="J224"/>
       <c r="O224" t="s">
         <v>612</v>
       </c>
@@ -10201,7 +10038,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="225" spans="1:20">
+    <row r="225" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B225" s="3">
         <v>429018903</v>
       </c>
@@ -10223,7 +10060,6 @@
       <c r="I225" t="s">
         <v>570</v>
       </c>
-      <c r="J225"/>
       <c r="O225" t="s">
         <v>612</v>
       </c>
@@ -10231,7 +10067,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="226" spans="1:20">
+    <row r="226" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B226" s="3">
         <v>313126401</v>
       </c>
@@ -10263,7 +10099,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="227" spans="1:20">
+    <row r="227" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B227" s="3">
         <v>320046101</v>
       </c>
@@ -10285,7 +10121,6 @@
       <c r="I227" t="s">
         <v>570</v>
       </c>
-      <c r="J227"/>
       <c r="O227" t="s">
         <v>612</v>
       </c>
@@ -10293,7 +10128,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="228" spans="1:20">
+    <row r="228" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B228" s="3">
         <v>418078701</v>
       </c>
@@ -10325,7 +10160,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="229" spans="1:20">
+    <row r="229" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B229" s="3">
         <v>603038002</v>
       </c>
@@ -10347,7 +10182,6 @@
       <c r="I229" t="s">
         <v>580</v>
       </c>
-      <c r="J229"/>
       <c r="O229" t="s">
         <v>612</v>
       </c>
@@ -10355,7 +10189,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="230" spans="1:20">
+    <row r="230" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B230" s="3">
         <v>415039101</v>
       </c>
@@ -10377,7 +10211,6 @@
       <c r="I230" t="s">
         <v>580</v>
       </c>
-      <c r="J230"/>
       <c r="O230" t="s">
         <v>612</v>
       </c>
@@ -10385,7 +10218,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="231" spans="1:20">
+    <row r="231" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B231" s="3">
         <v>401117901</v>
       </c>
@@ -10407,7 +10240,6 @@
       <c r="I231" t="s">
         <v>25</v>
       </c>
-      <c r="J231"/>
       <c r="O231" t="s">
         <v>612</v>
       </c>
@@ -10415,7 +10247,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="232" spans="1:20">
+    <row r="232" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B232" s="3">
         <v>419078903</v>
       </c>
@@ -10437,7 +10269,6 @@
       <c r="I232" t="s">
         <v>25</v>
       </c>
-      <c r="J232"/>
       <c r="O232" t="s">
         <v>612</v>
       </c>
@@ -10445,7 +10276,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="233" spans="1:20">
+    <row r="233" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B233" s="3">
         <v>430119102</v>
       </c>
@@ -10467,7 +10298,6 @@
       <c r="I233" t="s">
         <v>580</v>
       </c>
-      <c r="J233"/>
       <c r="O233" t="s">
         <v>612</v>
       </c>
@@ -10475,7 +10305,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="234" spans="1:20">
+    <row r="234" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B234" s="3">
         <v>415016301</v>
       </c>
@@ -10497,7 +10327,6 @@
       <c r="I234" t="s">
         <v>556</v>
       </c>
-      <c r="J234"/>
       <c r="O234" t="s">
         <v>613</v>
       </c>
@@ -10505,7 +10334,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="235" spans="1:20">
+    <row r="235" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B235" s="3">
         <v>324108103</v>
       </c>
@@ -10527,7 +10356,6 @@
       <c r="I235" t="s">
         <v>25</v>
       </c>
-      <c r="J235"/>
       <c r="O235" t="s">
         <v>613</v>
       </c>
@@ -10535,7 +10363,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="236" spans="1:20">
+    <row r="236" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B236" s="3">
         <v>406039002</v>
       </c>
@@ -10557,7 +10385,6 @@
       <c r="I236" t="s">
         <v>562</v>
       </c>
-      <c r="J236"/>
       <c r="O236" t="s">
         <v>613</v>
       </c>
@@ -10565,7 +10392,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="237" spans="1:20">
+    <row r="237" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B237" s="3">
         <v>409047703</v>
       </c>
@@ -10587,7 +10414,6 @@
       <c r="I237" t="s">
         <v>564</v>
       </c>
-      <c r="J237"/>
       <c r="O237" t="s">
         <v>613</v>
       </c>
@@ -10595,7 +10421,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="238" spans="1:20">
+    <row r="238" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B238" s="3">
         <v>427057407</v>
       </c>
@@ -10617,7 +10443,6 @@
       <c r="I238" t="s">
         <v>567</v>
       </c>
-      <c r="J238"/>
       <c r="O238" t="s">
         <v>613</v>
       </c>
@@ -10625,7 +10450,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="239" spans="1:20">
+    <row r="239" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B239" s="3">
         <v>428038302</v>
       </c>
@@ -10647,7 +10472,6 @@
       <c r="I239" t="s">
         <v>570</v>
       </c>
-      <c r="J239"/>
       <c r="O239" t="s">
         <v>613</v>
       </c>
@@ -10655,7 +10479,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="240" spans="1:20">
+    <row r="240" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B240" s="3">
         <v>406068904</v>
       </c>
@@ -10677,7 +10501,6 @@
       <c r="I240" t="s">
         <v>562</v>
       </c>
-      <c r="J240"/>
       <c r="O240" t="s">
         <v>613</v>
       </c>
@@ -10685,7 +10508,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="241" spans="1:20">
+    <row r="241" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B241" s="3">
         <v>2104066201</v>
       </c>
@@ -10717,7 +10540,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="242" spans="1:20">
+    <row r="242" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B242" s="3">
         <v>307069501</v>
       </c>
@@ -10749,7 +10572,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="243" spans="1:20">
+    <row r="243" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B243" s="3">
         <v>416098301</v>
       </c>
@@ -10771,7 +10594,6 @@
       <c r="I243" t="s">
         <v>580</v>
       </c>
-      <c r="J243"/>
       <c r="O243" t="s">
         <v>613</v>
       </c>
@@ -10779,7 +10601,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="244" spans="1:20">
+    <row r="244" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B244" s="3">
         <v>109118101</v>
       </c>
@@ -10811,7 +10633,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="245" spans="1:20">
+    <row r="245" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B245" s="3">
         <v>607079301</v>
       </c>
@@ -10833,7 +10655,6 @@
       <c r="I245" t="s">
         <v>583</v>
       </c>
-      <c r="J245"/>
       <c r="O245" t="s">
         <v>613</v>
       </c>
@@ -10841,7 +10662,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="246" spans="1:20">
+    <row r="246" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B246" s="3">
         <v>428118601</v>
       </c>
@@ -10873,7 +10694,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="247" spans="1:20">
+    <row r="247" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B247" s="3">
         <v>402019003</v>
       </c>
@@ -10895,7 +10716,6 @@
       <c r="I247" t="s">
         <v>562</v>
       </c>
-      <c r="J247"/>
       <c r="O247" t="s">
         <v>613</v>
       </c>
@@ -10903,7 +10723,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="248" spans="1:20">
+    <row r="248" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B248" s="3">
         <v>416069101</v>
       </c>
@@ -10925,7 +10745,6 @@
       <c r="I248" t="s">
         <v>570</v>
       </c>
-      <c r="J248"/>
       <c r="O248" t="s">
         <v>613</v>
       </c>
@@ -10933,7 +10752,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="249" spans="1:20">
+    <row r="249" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B249" s="3">
         <v>429018903</v>
       </c>
@@ -10955,7 +10774,6 @@
       <c r="I249" t="s">
         <v>570</v>
       </c>
-      <c r="J249"/>
       <c r="O249" t="s">
         <v>613</v>
       </c>
@@ -10963,7 +10781,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="250" spans="1:20">
+    <row r="250" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B250" s="3">
         <v>313126401</v>
       </c>
@@ -10995,7 +10813,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="251" spans="1:20">
+    <row r="251" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B251" s="3">
         <v>320046101</v>
       </c>
@@ -11017,7 +10835,6 @@
       <c r="I251" t="s">
         <v>570</v>
       </c>
-      <c r="J251"/>
       <c r="O251" t="s">
         <v>613</v>
       </c>
@@ -11025,7 +10842,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="252" spans="1:20">
+    <row r="252" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B252" s="3">
         <v>418078701</v>
       </c>
@@ -11057,7 +10874,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="253" spans="1:20">
+    <row r="253" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B253" s="3">
         <v>603038002</v>
       </c>
@@ -11079,7 +10896,6 @@
       <c r="I253" t="s">
         <v>580</v>
       </c>
-      <c r="J253"/>
       <c r="O253" t="s">
         <v>613</v>
       </c>
@@ -11087,7 +10903,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="254" spans="1:20">
+    <row r="254" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B254" s="3">
         <v>415039101</v>
       </c>
@@ -11109,7 +10925,6 @@
       <c r="I254" t="s">
         <v>580</v>
       </c>
-      <c r="J254"/>
       <c r="O254" t="s">
         <v>613</v>
       </c>
@@ -11117,7 +10932,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="255" spans="1:20">
+    <row r="255" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B255" s="3">
         <v>401117901</v>
       </c>
@@ -11139,7 +10954,6 @@
       <c r="I255" t="s">
         <v>25</v>
       </c>
-      <c r="J255"/>
       <c r="O255" t="s">
         <v>613</v>
       </c>
@@ -11147,7 +10961,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="256" spans="1:20">
+    <row r="256" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B256" s="3">
         <v>419078903</v>
       </c>
@@ -11169,7 +10983,6 @@
       <c r="I256" t="s">
         <v>25</v>
       </c>
-      <c r="J256"/>
       <c r="O256" t="s">
         <v>613</v>
       </c>
@@ -11177,7 +10990,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="257" spans="1:20">
+    <row r="257" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B257" s="3">
         <v>430119102</v>
       </c>
@@ -11199,7 +11012,6 @@
       <c r="I257" t="s">
         <v>580</v>
       </c>
-      <c r="J257"/>
       <c r="O257" t="s">
         <v>613</v>
       </c>
@@ -11207,7 +11019,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="258" spans="1:20">
+    <row r="258" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B258" s="3">
         <v>428078803</v>
       </c>
@@ -11229,7 +11041,6 @@
       <c r="I258" t="s">
         <v>562</v>
       </c>
-      <c r="J258"/>
       <c r="O258" t="s">
         <v>613</v>
       </c>
@@ -11237,7 +11048,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="259" spans="1:20">
+    <row r="259" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B259" s="3">
         <v>628118902</v>
       </c>
@@ -11259,7 +11070,6 @@
       <c r="I259" t="s">
         <v>580</v>
       </c>
-      <c r="J259"/>
       <c r="O259" t="s">
         <v>613</v>
       </c>
@@ -11267,7 +11077,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="260" spans="1:20">
+    <row r="260" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B260" s="3">
         <v>420088503</v>
       </c>
@@ -11299,7 +11109,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="261" spans="1:20">
+    <row r="261" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B261" s="3">
         <v>428118904</v>
       </c>
@@ -11321,7 +11131,6 @@
       <c r="I261" t="s">
         <v>570</v>
       </c>
-      <c r="J261"/>
       <c r="O261" t="s">
         <v>613</v>
       </c>
@@ -11329,7 +11138,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="262" spans="1:20">
+    <row r="262" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B262" s="3">
         <v>415028303</v>
       </c>
@@ -11351,7 +11160,6 @@
       <c r="I262" t="s">
         <v>603</v>
       </c>
-      <c r="J262"/>
       <c r="O262" t="s">
         <v>613</v>
       </c>
@@ -11359,7 +11167,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="263" spans="1:20">
+    <row r="263" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B263" s="3">
         <v>2928037201</v>
       </c>
@@ -11391,7 +11199,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="264" spans="1:20">
+    <row r="264" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B264" s="3">
         <v>420087402</v>
       </c>
@@ -11413,7 +11221,6 @@
       <c r="I264" t="s">
         <v>570</v>
       </c>
-      <c r="J264"/>
       <c r="O264" t="s">
         <v>613</v>
       </c>
@@ -11421,7 +11228,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="265" spans="1:20">
+    <row r="265" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B265" s="3">
         <v>306046502</v>
       </c>
@@ -11443,7 +11250,6 @@
       <c r="I265" t="s">
         <v>25</v>
       </c>
-      <c r="J265"/>
       <c r="O265" t="s">
         <v>613</v>
       </c>
@@ -11451,7 +11257,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="266" spans="1:20">
+    <row r="266" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B266" s="3">
         <v>430079201</v>
       </c>
@@ -11473,7 +11279,6 @@
       <c r="I266" t="s">
         <v>564</v>
       </c>
-      <c r="J266"/>
       <c r="O266" t="s">
         <v>613</v>
       </c>
@@ -11481,7 +11286,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="267" spans="1:20">
+    <row r="267" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B267" s="3">
         <v>430068301</v>
       </c>
@@ -11503,7 +11308,6 @@
       <c r="I267" t="s">
         <v>562</v>
       </c>
-      <c r="J267"/>
       <c r="O267" t="s">
         <v>613</v>
       </c>
@@ -11511,7 +11315,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="268" spans="1:20">
+    <row r="268" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B268" s="3">
         <v>415016301</v>
       </c>
@@ -11533,7 +11337,6 @@
       <c r="I268" t="s">
         <v>556</v>
       </c>
-      <c r="J268"/>
       <c r="O268" t="s">
         <v>211</v>
       </c>
@@ -11541,7 +11344,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="269" spans="1:20">
+    <row r="269" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B269" s="3">
         <v>324108103</v>
       </c>
@@ -11563,7 +11366,6 @@
       <c r="I269" t="s">
         <v>25</v>
       </c>
-      <c r="J269"/>
       <c r="O269" t="s">
         <v>211</v>
       </c>
@@ -11571,7 +11373,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="270" spans="1:20">
+    <row r="270" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B270" s="3">
         <v>406039002</v>
       </c>
@@ -11593,7 +11395,6 @@
       <c r="I270" t="s">
         <v>562</v>
       </c>
-      <c r="J270"/>
       <c r="O270" t="s">
         <v>211</v>
       </c>
@@ -11601,7 +11402,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="271" spans="1:20">
+    <row r="271" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B271" s="3">
         <v>409047703</v>
       </c>
@@ -11623,7 +11424,6 @@
       <c r="I271" t="s">
         <v>564</v>
       </c>
-      <c r="J271"/>
       <c r="O271" t="s">
         <v>211</v>
       </c>
@@ -11631,7 +11431,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="272" spans="1:20">
+    <row r="272" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B272" s="3">
         <v>427057407</v>
       </c>
@@ -11653,7 +11453,6 @@
       <c r="I272" t="s">
         <v>567</v>
       </c>
-      <c r="J272"/>
       <c r="O272" t="s">
         <v>211</v>
       </c>
@@ -11661,7 +11460,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="273" spans="1:20">
+    <row r="273" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B273" s="3">
         <v>428038302</v>
       </c>
@@ -11683,7 +11482,6 @@
       <c r="I273" t="s">
         <v>570</v>
       </c>
-      <c r="J273"/>
       <c r="O273" t="s">
         <v>211</v>
       </c>
@@ -11691,7 +11489,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="274" spans="1:20">
+    <row r="274" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B274" s="3">
         <v>406068904</v>
       </c>
@@ -11713,7 +11511,6 @@
       <c r="I274" t="s">
         <v>562</v>
       </c>
-      <c r="J274"/>
       <c r="O274" t="s">
         <v>211</v>
       </c>
@@ -11721,13 +11518,10 @@
         <v>614</v>
       </c>
     </row>
-    <row r="275" spans="1:20">
+    <row r="275" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B275" s="3">
         <v>2104066201</v>
       </c>
-      <c r="C275" s="3">
-        <v>0</v>
-      </c>
       <c r="D275" t="s">
         <v>197</v>
       </c>
@@ -11756,7 +11550,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="276" spans="1:20">
+    <row r="276" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B276" s="3">
         <v>307069501</v>
       </c>
@@ -11788,12 +11582,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="277" spans="1:20">
+    <row r="277" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B277" s="3">
         <v>416098301</v>
       </c>
-      <c r="C277" s="3">
-        <v>3248761661300003</v>
+      <c r="C277" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="D277" t="s">
         <v>578</v>
@@ -11813,7 +11607,6 @@
       <c r="I277" t="s">
         <v>580</v>
       </c>
-      <c r="J277"/>
       <c r="O277" t="s">
         <v>211</v>
       </c>
@@ -11821,13 +11614,10 @@
         <v>614</v>
       </c>
     </row>
-    <row r="278" spans="1:20">
+    <row r="278" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B278" s="3">
         <v>109118101</v>
       </c>
-      <c r="C278" s="3">
-        <v>0</v>
-      </c>
       <c r="D278" t="s">
         <v>581</v>
       </c>
@@ -11856,7 +11646,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="279" spans="1:20">
+    <row r="279" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B279" s="3">
         <v>607079301</v>
       </c>
@@ -11878,7 +11668,6 @@
       <c r="I279" t="s">
         <v>583</v>
       </c>
-      <c r="J279"/>
       <c r="O279" t="s">
         <v>211</v>
       </c>
@@ -11886,12 +11675,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="280" spans="1:20">
+    <row r="280" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B280" s="3">
         <v>428118601</v>
       </c>
-      <c r="C280" s="3">
-        <v>2460764665230233</v>
+      <c r="C280" s="3" t="s">
+        <v>711</v>
       </c>
       <c r="D280" t="s">
         <v>319</v>
@@ -11921,7 +11710,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="281" spans="1:20">
+    <row r="281" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B281" s="3">
         <v>402019003</v>
       </c>
@@ -11943,7 +11732,6 @@
       <c r="I281" t="s">
         <v>562</v>
       </c>
-      <c r="J281"/>
       <c r="O281" t="s">
         <v>211</v>
       </c>
@@ -11951,7 +11739,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="282" spans="1:20">
+    <row r="282" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B282" s="3">
         <v>416069101</v>
       </c>
@@ -11973,7 +11761,6 @@
       <c r="I282" t="s">
         <v>570</v>
       </c>
-      <c r="J282"/>
       <c r="O282" t="s">
         <v>211</v>
       </c>
@@ -11981,7 +11768,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="283" spans="1:20">
+    <row r="283" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B283" s="3">
         <v>429018903</v>
       </c>
@@ -12003,7 +11790,6 @@
       <c r="I283" t="s">
         <v>570</v>
       </c>
-      <c r="J283"/>
       <c r="O283" t="s">
         <v>211</v>
       </c>
@@ -12011,12 +11797,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="284" spans="1:20">
+    <row r="284" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B284" s="3">
         <v>313126401</v>
       </c>
-      <c r="C284" s="3">
-        <v>3674030312640003</v>
+      <c r="C284" s="3" t="s">
+        <v>712</v>
       </c>
       <c r="D284" t="s">
         <v>470</v>
@@ -12046,7 +11832,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="285" spans="1:20">
+    <row r="285" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B285" s="3">
         <v>320046101</v>
       </c>
@@ -12068,7 +11854,6 @@
       <c r="I285" t="s">
         <v>570</v>
       </c>
-      <c r="J285"/>
       <c r="O285" t="s">
         <v>211</v>
       </c>
@@ -12076,12 +11861,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="286" spans="1:20">
+    <row r="286" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B286" s="3">
         <v>418078701</v>
       </c>
-      <c r="C286" s="3">
-        <v>2050765666230343</v>
+      <c r="C286" s="3" t="s">
+        <v>713</v>
       </c>
       <c r="D286" t="s">
         <v>588</v>
@@ -12111,7 +11896,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="287" spans="1:20">
+    <row r="287" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B287" s="3">
         <v>603038002</v>
       </c>
@@ -12133,7 +11918,6 @@
       <c r="I287" t="s">
         <v>580</v>
       </c>
-      <c r="J287"/>
       <c r="O287" t="s">
         <v>211</v>
       </c>
@@ -12141,7 +11925,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="288" spans="1:20">
+    <row r="288" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B288" s="3">
         <v>415039101</v>
       </c>
@@ -12163,7 +11947,6 @@
       <c r="I288" t="s">
         <v>580</v>
       </c>
-      <c r="J288"/>
       <c r="O288" t="s">
         <v>211</v>
       </c>
@@ -12171,7 +11954,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="289" spans="1:20">
+    <row r="289" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B289" s="3">
         <v>401117901</v>
       </c>
@@ -12193,7 +11976,6 @@
       <c r="I289" t="s">
         <v>25</v>
       </c>
-      <c r="J289"/>
       <c r="O289" t="s">
         <v>211</v>
       </c>
@@ -12201,7 +11983,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="290" spans="1:20">
+    <row r="290" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B290" s="3">
         <v>419078903</v>
       </c>
@@ -12223,7 +12005,6 @@
       <c r="I290" t="s">
         <v>25</v>
       </c>
-      <c r="J290"/>
       <c r="O290" t="s">
         <v>211</v>
       </c>
@@ -12231,7 +12012,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="291" spans="1:20">
+    <row r="291" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B291" s="3">
         <v>430119102</v>
       </c>
@@ -12253,7 +12034,6 @@
       <c r="I291" t="s">
         <v>580</v>
       </c>
-      <c r="J291"/>
       <c r="O291" t="s">
         <v>211</v>
       </c>
@@ -12261,7 +12041,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="292" spans="1:20">
+    <row r="292" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B292" s="3">
         <v>428078803</v>
       </c>
@@ -12283,7 +12063,6 @@
       <c r="I292" t="s">
         <v>562</v>
       </c>
-      <c r="J292"/>
       <c r="O292" t="s">
         <v>211</v>
       </c>
@@ -12291,7 +12070,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="293" spans="1:20">
+    <row r="293" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B293" s="3">
         <v>628118902</v>
       </c>
@@ -12313,7 +12092,6 @@
       <c r="I293" t="s">
         <v>580</v>
       </c>
-      <c r="J293"/>
       <c r="O293" t="s">
         <v>211</v>
       </c>
@@ -12321,7 +12099,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="294" spans="1:20">
+    <row r="294" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B294" s="3">
         <v>420088503</v>
       </c>
@@ -12353,7 +12131,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="295" spans="1:20">
+    <row r="295" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B295" s="3">
         <v>428118904</v>
       </c>
@@ -12375,7 +12153,6 @@
       <c r="I295" t="s">
         <v>570</v>
       </c>
-      <c r="J295"/>
       <c r="O295" t="s">
         <v>211</v>
       </c>
@@ -12383,7 +12160,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="296" spans="1:20">
+    <row r="296" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B296" s="3">
         <v>415028303</v>
       </c>
@@ -12405,7 +12182,6 @@
       <c r="I296" t="s">
         <v>603</v>
       </c>
-      <c r="J296"/>
       <c r="O296" t="s">
         <v>211</v>
       </c>
@@ -12413,12 +12189,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="297" spans="1:20">
+    <row r="297" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B297" s="3">
         <v>2928037201</v>
       </c>
-      <c r="C297" s="3">
-        <v>6660750651130072</v>
+      <c r="C297" s="3" t="s">
+        <v>714</v>
       </c>
       <c r="D297" t="s">
         <v>604</v>
@@ -12448,7 +12224,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="298" spans="1:20">
+    <row r="298" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B298" s="3">
         <v>420087402</v>
       </c>
@@ -12470,7 +12246,6 @@
       <c r="I298" t="s">
         <v>570</v>
       </c>
-      <c r="J298"/>
       <c r="O298" t="s">
         <v>211</v>
       </c>
@@ -12478,7 +12253,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="299" spans="1:20">
+    <row r="299" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B299" s="3">
         <v>306046502</v>
       </c>
@@ -12500,7 +12275,6 @@
       <c r="I299" t="s">
         <v>25</v>
       </c>
-      <c r="J299"/>
       <c r="O299" t="s">
         <v>211</v>
       </c>
@@ -12508,7 +12282,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="300" spans="1:20">
+    <row r="300" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B300" s="3">
         <v>430079201</v>
       </c>
@@ -12530,7 +12304,6 @@
       <c r="I300" t="s">
         <v>564</v>
       </c>
-      <c r="J300"/>
       <c r="O300" t="s">
         <v>211</v>
       </c>
@@ -12538,7 +12311,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="301" spans="1:20">
+    <row r="301" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B301" s="3">
         <v>430068301</v>
       </c>
@@ -12560,7 +12333,6 @@
       <c r="I301" t="s">
         <v>562</v>
       </c>
-      <c r="J301"/>
       <c r="O301" t="s">
         <v>211</v>
       </c>
@@ -12568,7 +12340,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="302" spans="1:20">
+    <row r="302" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B302" s="3">
         <v>415016301</v>
       </c>
@@ -12590,7 +12362,6 @@
       <c r="I302" t="s">
         <v>556</v>
       </c>
-      <c r="J302"/>
       <c r="O302" t="s">
         <v>209</v>
       </c>
@@ -12598,7 +12369,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="303" spans="1:20">
+    <row r="303" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B303" s="3">
         <v>324108103</v>
       </c>
@@ -12620,7 +12391,6 @@
       <c r="I303" t="s">
         <v>25</v>
       </c>
-      <c r="J303"/>
       <c r="O303" t="s">
         <v>209</v>
       </c>
@@ -12628,7 +12398,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="304" spans="1:20">
+    <row r="304" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B304" s="3">
         <v>406039002</v>
       </c>
@@ -12650,7 +12420,6 @@
       <c r="I304" t="s">
         <v>562</v>
       </c>
-      <c r="J304"/>
       <c r="O304" t="s">
         <v>209</v>
       </c>
@@ -12658,7 +12427,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="305" spans="1:20">
+    <row r="305" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B305" s="3">
         <v>409047703</v>
       </c>
@@ -12680,7 +12449,6 @@
       <c r="I305" t="s">
         <v>564</v>
       </c>
-      <c r="J305"/>
       <c r="O305" t="s">
         <v>209</v>
       </c>
@@ -12688,7 +12456,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="306" spans="1:20">
+    <row r="306" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B306" s="3">
         <v>427057407</v>
       </c>
@@ -12710,7 +12478,6 @@
       <c r="I306" t="s">
         <v>567</v>
       </c>
-      <c r="J306"/>
       <c r="O306" t="s">
         <v>209</v>
       </c>
@@ -12718,7 +12485,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="307" spans="1:20">
+    <row r="307" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B307" s="3">
         <v>428038302</v>
       </c>
@@ -12740,7 +12507,6 @@
       <c r="I307" t="s">
         <v>570</v>
       </c>
-      <c r="J307"/>
       <c r="O307" t="s">
         <v>209</v>
       </c>
@@ -12748,7 +12514,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="308" spans="1:20">
+    <row r="308" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B308" s="3">
         <v>406068904</v>
       </c>
@@ -12770,7 +12536,6 @@
       <c r="I308" t="s">
         <v>562</v>
       </c>
-      <c r="J308"/>
       <c r="O308" t="s">
         <v>209</v>
       </c>
@@ -12778,13 +12543,10 @@
         <v>614</v>
       </c>
     </row>
-    <row r="309" spans="1:20">
+    <row r="309" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B309" s="3">
         <v>2104066201</v>
       </c>
-      <c r="C309" s="3">
-        <v>0</v>
-      </c>
       <c r="D309" t="s">
         <v>197</v>
       </c>
@@ -12813,7 +12575,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="310" spans="1:20">
+    <row r="310" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B310" s="3">
         <v>307069501</v>
       </c>
@@ -12845,12 +12607,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="311" spans="1:20">
+    <row r="311" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B311" s="3">
         <v>416098301</v>
       </c>
-      <c r="C311" s="3">
-        <v>3248761661300003</v>
+      <c r="C311" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="D311" t="s">
         <v>578</v>
@@ -12870,7 +12632,6 @@
       <c r="I311" t="s">
         <v>580</v>
       </c>
-      <c r="J311"/>
       <c r="O311" t="s">
         <v>209</v>
       </c>
@@ -12878,13 +12639,10 @@
         <v>614</v>
       </c>
     </row>
-    <row r="312" spans="1:20">
+    <row r="312" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B312" s="3">
         <v>109118101</v>
       </c>
-      <c r="C312" s="3">
-        <v>0</v>
-      </c>
       <c r="D312" t="s">
         <v>581</v>
       </c>
@@ -12913,7 +12671,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="313" spans="1:20">
+    <row r="313" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B313" s="3">
         <v>607079301</v>
       </c>
@@ -12935,7 +12693,6 @@
       <c r="I313" t="s">
         <v>583</v>
       </c>
-      <c r="J313"/>
       <c r="O313" t="s">
         <v>209</v>
       </c>
@@ -12943,12 +12700,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="314" spans="1:20">
+    <row r="314" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B314" s="3">
         <v>428118601</v>
       </c>
-      <c r="C314" s="3">
-        <v>2460764665230233</v>
+      <c r="C314" s="3" t="s">
+        <v>711</v>
       </c>
       <c r="D314" t="s">
         <v>319</v>
@@ -12978,7 +12735,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="315" spans="1:20">
+    <row r="315" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B315" s="3">
         <v>402019003</v>
       </c>
@@ -13000,7 +12757,6 @@
       <c r="I315" t="s">
         <v>562</v>
       </c>
-      <c r="J315"/>
       <c r="O315" t="s">
         <v>209</v>
       </c>
@@ -13008,7 +12764,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="316" spans="1:20">
+    <row r="316" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B316" s="3">
         <v>416069101</v>
       </c>
@@ -13030,7 +12786,6 @@
       <c r="I316" t="s">
         <v>570</v>
       </c>
-      <c r="J316"/>
       <c r="O316" t="s">
         <v>209</v>
       </c>
@@ -13038,7 +12793,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="317" spans="1:20">
+    <row r="317" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B317" s="3">
         <v>429018903</v>
       </c>
@@ -13060,7 +12815,6 @@
       <c r="I317" t="s">
         <v>570</v>
       </c>
-      <c r="J317"/>
       <c r="O317" t="s">
         <v>209</v>
       </c>
@@ -13068,12 +12822,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="318" spans="1:20">
+    <row r="318" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B318" s="3">
         <v>313126401</v>
       </c>
-      <c r="C318" s="3">
-        <v>3674030312640003</v>
+      <c r="C318" s="3" t="s">
+        <v>712</v>
       </c>
       <c r="D318" t="s">
         <v>470</v>
@@ -13103,7 +12857,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="319" spans="1:20">
+    <row r="319" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B319" s="3">
         <v>320046101</v>
       </c>
@@ -13125,7 +12879,6 @@
       <c r="I319" t="s">
         <v>570</v>
       </c>
-      <c r="J319"/>
       <c r="O319" t="s">
         <v>209</v>
       </c>
@@ -13133,12 +12886,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="320" spans="1:20">
+    <row r="320" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B320" s="3">
         <v>418078701</v>
       </c>
-      <c r="C320" s="3">
-        <v>2050765666230343</v>
+      <c r="C320" s="3" t="s">
+        <v>713</v>
       </c>
       <c r="D320" t="s">
         <v>588</v>
@@ -13168,7 +12921,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="321" spans="1:20">
+    <row r="321" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B321" s="3">
         <v>603038002</v>
       </c>
@@ -13190,7 +12943,6 @@
       <c r="I321" t="s">
         <v>580</v>
       </c>
-      <c r="J321"/>
       <c r="O321" t="s">
         <v>209</v>
       </c>
@@ -13198,7 +12950,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="322" spans="1:20">
+    <row r="322" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B322" s="3">
         <v>415039101</v>
       </c>
@@ -13220,7 +12972,6 @@
       <c r="I322" t="s">
         <v>580</v>
       </c>
-      <c r="J322"/>
       <c r="O322" t="s">
         <v>209</v>
       </c>
@@ -13228,7 +12979,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="323" spans="1:20">
+    <row r="323" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B323" s="3">
         <v>401117901</v>
       </c>
@@ -13250,7 +13001,6 @@
       <c r="I323" t="s">
         <v>25</v>
       </c>
-      <c r="J323"/>
       <c r="O323" t="s">
         <v>209</v>
       </c>
@@ -13258,7 +13008,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="324" spans="1:20">
+    <row r="324" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B324" s="3">
         <v>419078903</v>
       </c>
@@ -13280,7 +13030,6 @@
       <c r="I324" t="s">
         <v>25</v>
       </c>
-      <c r="J324"/>
       <c r="O324" t="s">
         <v>209</v>
       </c>
@@ -13288,7 +13037,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="325" spans="1:20">
+    <row r="325" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B325" s="3">
         <v>430119102</v>
       </c>
@@ -13310,7 +13059,6 @@
       <c r="I325" t="s">
         <v>580</v>
       </c>
-      <c r="J325"/>
       <c r="O325" t="s">
         <v>209</v>
       </c>
@@ -13318,7 +13066,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="326" spans="1:20">
+    <row r="326" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B326" s="3">
         <v>428078803</v>
       </c>
@@ -13340,7 +13088,6 @@
       <c r="I326" t="s">
         <v>562</v>
       </c>
-      <c r="J326"/>
       <c r="O326" t="s">
         <v>209</v>
       </c>
@@ -13348,7 +13095,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="327" spans="1:20">
+    <row r="327" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B327" s="3">
         <v>628118902</v>
       </c>
@@ -13370,7 +13117,6 @@
       <c r="I327" t="s">
         <v>580</v>
       </c>
-      <c r="J327"/>
       <c r="O327" t="s">
         <v>209</v>
       </c>
@@ -13378,7 +13124,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="328" spans="1:20">
+    <row r="328" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B328" s="3">
         <v>420088503</v>
       </c>
@@ -13410,7 +13156,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="329" spans="1:20">
+    <row r="329" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B329" s="3">
         <v>428118904</v>
       </c>
@@ -13432,7 +13178,6 @@
       <c r="I329" t="s">
         <v>570</v>
       </c>
-      <c r="J329"/>
       <c r="O329" t="s">
         <v>209</v>
       </c>
@@ -13440,7 +13185,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="330" spans="1:20">
+    <row r="330" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B330" s="3">
         <v>415028303</v>
       </c>
@@ -13462,7 +13207,6 @@
       <c r="I330" t="s">
         <v>603</v>
       </c>
-      <c r="J330"/>
       <c r="O330" t="s">
         <v>209</v>
       </c>
@@ -13470,12 +13214,12 @@
         <v>614</v>
       </c>
     </row>
-    <row r="331" spans="1:20">
+    <row r="331" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B331" s="3">
         <v>2928037201</v>
       </c>
-      <c r="C331" s="3">
-        <v>6660750651130072</v>
+      <c r="C331" s="3" t="s">
+        <v>714</v>
       </c>
       <c r="D331" t="s">
         <v>604</v>
@@ -13505,7 +13249,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="332" spans="1:20">
+    <row r="332" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B332" s="3">
         <v>420087402</v>
       </c>
@@ -13527,7 +13271,6 @@
       <c r="I332" t="s">
         <v>570</v>
       </c>
-      <c r="J332"/>
       <c r="O332" t="s">
         <v>209</v>
       </c>
@@ -13535,7 +13278,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="333" spans="1:20">
+    <row r="333" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B333" s="3">
         <v>306046502</v>
       </c>
@@ -13557,7 +13300,6 @@
       <c r="I333" t="s">
         <v>25</v>
       </c>
-      <c r="J333"/>
       <c r="O333" t="s">
         <v>209</v>
       </c>
@@ -13565,7 +13307,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="334" spans="1:20">
+    <row r="334" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B334" s="3">
         <v>430079201</v>
       </c>
@@ -13587,7 +13329,6 @@
       <c r="I334" t="s">
         <v>564</v>
       </c>
-      <c r="J334"/>
       <c r="O334" t="s">
         <v>209</v>
       </c>
@@ -13595,7 +13336,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="335" spans="1:20">
+    <row r="335" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B335" s="3">
         <v>430068301</v>
       </c>
@@ -13617,7 +13358,6 @@
       <c r="I335" t="s">
         <v>562</v>
       </c>
-      <c r="J335"/>
       <c r="O335" t="s">
         <v>209</v>
       </c>
@@ -13625,7 +13365,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="336" spans="1:20">
+    <row r="336" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B336" s="3">
         <v>405068601</v>
       </c>
@@ -13647,7 +13387,6 @@
       <c r="I336" t="s">
         <v>562</v>
       </c>
-      <c r="J336"/>
       <c r="O336" t="s">
         <v>617</v>
       </c>
@@ -13655,7 +13394,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="337" spans="1:20">
+    <row r="337" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B337" s="3">
         <v>431038302</v>
       </c>
@@ -13677,7 +13416,6 @@
       <c r="I337" t="s">
         <v>562</v>
       </c>
-      <c r="J337"/>
       <c r="O337" t="s">
         <v>617</v>
       </c>
@@ -13685,7 +13423,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="338" spans="1:20">
+    <row r="338" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B338" s="3">
         <v>405027903</v>
       </c>
@@ -13707,7 +13445,6 @@
       <c r="I338" t="s">
         <v>25</v>
       </c>
-      <c r="J338"/>
       <c r="O338" t="s">
         <v>617</v>
       </c>
@@ -13715,7 +13452,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="339" spans="1:20">
+    <row r="339" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B339" s="3">
         <v>416077201</v>
       </c>
@@ -13737,7 +13474,6 @@
       <c r="I339" t="s">
         <v>24</v>
       </c>
-      <c r="J339"/>
       <c r="O339" t="s">
         <v>617</v>
       </c>
@@ -13745,12 +13481,12 @@
         <v>618</v>
       </c>
     </row>
-    <row r="340" spans="1:20">
+    <row r="340" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B340" s="3">
         <v>425127501</v>
       </c>
-      <c r="C340" s="3">
-        <v>1557753654230183</v>
+      <c r="C340" s="3" t="s">
+        <v>719</v>
       </c>
       <c r="D340" t="s">
         <v>624</v>
@@ -13780,7 +13516,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="341" spans="1:20">
+    <row r="341" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B341" s="3">
         <v>403027202</v>
       </c>
@@ -13802,7 +13538,6 @@
       <c r="I341" t="s">
         <v>25</v>
       </c>
-      <c r="J341"/>
       <c r="O341" t="s">
         <v>617</v>
       </c>
@@ -13810,7 +13545,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="342" spans="1:20">
+    <row r="342" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B342" s="3">
         <v>417038601</v>
       </c>
@@ -13832,7 +13567,6 @@
       <c r="I342" t="s">
         <v>603</v>
       </c>
-      <c r="J342"/>
       <c r="O342" t="s">
         <v>617</v>
       </c>
@@ -13840,7 +13574,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="343" spans="1:20">
+    <row r="343" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B343" s="3">
         <v>420117202</v>
       </c>
@@ -13862,7 +13596,6 @@
       <c r="I343" t="s">
         <v>562</v>
       </c>
-      <c r="J343"/>
       <c r="O343" t="s">
         <v>617</v>
       </c>
@@ -13870,7 +13603,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="344" spans="1:20">
+    <row r="344" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B344" s="3">
         <v>103078600</v>
       </c>
@@ -13892,7 +13625,6 @@
       <c r="I344" t="s">
         <v>634</v>
       </c>
-      <c r="J344"/>
       <c r="O344" t="s">
         <v>617</v>
       </c>
@@ -13900,12 +13632,12 @@
         <v>618</v>
       </c>
     </row>
-    <row r="345" spans="1:20">
+    <row r="345" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B345" s="3">
         <v>415049105</v>
       </c>
-      <c r="C345" s="3">
-        <v>2747769670130402</v>
+      <c r="C345" s="3" t="s">
+        <v>718</v>
       </c>
       <c r="D345" t="s">
         <v>635</v>
@@ -13935,7 +13667,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="346" spans="1:20">
+    <row r="346" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B346" s="3">
         <v>419028603</v>
       </c>
@@ -13957,7 +13689,6 @@
       <c r="I346" t="s">
         <v>562</v>
       </c>
-      <c r="J346"/>
       <c r="O346" t="s">
         <v>617</v>
       </c>
@@ -13965,7 +13696,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="347" spans="1:20">
+    <row r="347" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B347" s="3">
         <v>409048607</v>
       </c>
@@ -13987,7 +13718,6 @@
       <c r="I347" t="s">
         <v>570</v>
       </c>
-      <c r="J347"/>
       <c r="O347" t="s">
         <v>617</v>
       </c>
@@ -13995,7 +13725,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="348" spans="1:20">
+    <row r="348" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B348" s="3">
         <v>420096903</v>
       </c>
@@ -14017,7 +13747,6 @@
       <c r="I348" t="s">
         <v>603</v>
       </c>
-      <c r="J348"/>
       <c r="O348" t="s">
         <v>617</v>
       </c>
@@ -14025,7 +13754,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="349" spans="1:20">
+    <row r="349" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B349" s="3">
         <v>405128601</v>
       </c>
@@ -14047,7 +13776,6 @@
       <c r="I349" t="s">
         <v>25</v>
       </c>
-      <c r="J349"/>
       <c r="O349" t="s">
         <v>617</v>
       </c>
@@ -14055,7 +13783,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="350" spans="1:20">
+    <row r="350" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B350" s="3">
         <v>429056701</v>
       </c>
@@ -14077,7 +13805,6 @@
       <c r="I350" t="s">
         <v>562</v>
       </c>
-      <c r="J350"/>
       <c r="O350" t="s">
         <v>617</v>
       </c>
@@ -14085,7 +13812,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="351" spans="1:20">
+    <row r="351" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B351" s="3">
         <v>417127902</v>
       </c>
@@ -14107,7 +13834,6 @@
       <c r="I351" t="s">
         <v>25</v>
       </c>
-      <c r="J351"/>
       <c r="O351" t="s">
         <v>617</v>
       </c>
@@ -14115,7 +13841,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="352" spans="1:20">
+    <row r="352" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B352" s="3">
         <v>406118803</v>
       </c>
@@ -14137,7 +13863,6 @@
       <c r="I352" t="s">
         <v>25</v>
       </c>
-      <c r="J352"/>
       <c r="O352" t="s">
         <v>617</v>
       </c>
@@ -14145,7 +13870,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="353" spans="1:20">
+    <row r="353" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B353" s="3">
         <v>413088004</v>
       </c>
@@ -14167,7 +13892,6 @@
       <c r="I353" t="s">
         <v>562</v>
       </c>
-      <c r="J353"/>
       <c r="O353" t="s">
         <v>617</v>
       </c>
@@ -14175,7 +13899,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="354" spans="1:20">
+    <row r="354" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B354" s="3">
         <v>420038901</v>
       </c>
@@ -14197,7 +13921,6 @@
       <c r="I354" t="s">
         <v>562</v>
       </c>
-      <c r="J354"/>
       <c r="O354" t="s">
         <v>617</v>
       </c>
@@ -14205,7 +13928,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="355" spans="1:20">
+    <row r="355" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B355" s="3">
         <v>412017503</v>
       </c>
@@ -14227,7 +13950,6 @@
       <c r="I355" t="s">
         <v>648</v>
       </c>
-      <c r="J355"/>
       <c r="O355" t="s">
         <v>617</v>
       </c>
@@ -14235,7 +13957,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="356" spans="1:20">
+    <row r="356" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B356" s="3">
         <v>418056801</v>
       </c>
@@ -14257,7 +13979,6 @@
       <c r="I356" t="s">
         <v>562</v>
       </c>
-      <c r="J356"/>
       <c r="O356" t="s">
         <v>617</v>
       </c>
@@ -14265,7 +13986,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="357" spans="1:20">
+    <row r="357" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B357" s="3">
         <v>409108602</v>
       </c>
@@ -14287,7 +14008,6 @@
       <c r="I357" t="s">
         <v>570</v>
       </c>
-      <c r="J357"/>
       <c r="O357" t="s">
         <v>617</v>
       </c>
@@ -14295,7 +14015,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="358" spans="1:20">
+    <row r="358" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B358" s="3">
         <v>416068101</v>
       </c>
@@ -14317,7 +14037,6 @@
       <c r="I358" t="s">
         <v>25</v>
       </c>
-      <c r="J358"/>
       <c r="O358" t="s">
         <v>617</v>
       </c>
@@ -14325,7 +14044,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="359" spans="1:20">
+    <row r="359" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B359" s="3">
         <v>405068601</v>
       </c>
@@ -14347,7 +14066,6 @@
       <c r="I359" t="s">
         <v>562</v>
       </c>
-      <c r="J359"/>
       <c r="O359" t="s">
         <v>652</v>
       </c>
@@ -14355,7 +14073,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="360" spans="1:20">
+    <row r="360" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B360" s="3">
         <v>431038302</v>
       </c>
@@ -14377,7 +14095,6 @@
       <c r="I360" t="s">
         <v>562</v>
       </c>
-      <c r="J360"/>
       <c r="O360" t="s">
         <v>652</v>
       </c>
@@ -14385,7 +14102,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="361" spans="1:20">
+    <row r="361" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B361" s="3">
         <v>405027903</v>
       </c>
@@ -14407,7 +14124,6 @@
       <c r="I361" t="s">
         <v>25</v>
       </c>
-      <c r="J361"/>
       <c r="O361" t="s">
         <v>652</v>
       </c>
@@ -14415,7 +14131,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="362" spans="1:20">
+    <row r="362" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B362" s="3">
         <v>416077201</v>
       </c>
@@ -14437,7 +14153,6 @@
       <c r="I362" t="s">
         <v>24</v>
       </c>
-      <c r="J362"/>
       <c r="O362" t="s">
         <v>652</v>
       </c>
@@ -14445,12 +14160,12 @@
         <v>653</v>
       </c>
     </row>
-    <row r="363" spans="1:20">
+    <row r="363" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B363" s="3">
         <v>425127501</v>
       </c>
-      <c r="C363" s="3">
-        <v>1557753654230183</v>
+      <c r="C363" s="3" t="s">
+        <v>719</v>
       </c>
       <c r="D363" t="s">
         <v>624</v>
@@ -14480,7 +14195,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="364" spans="1:20">
+    <row r="364" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B364" s="3">
         <v>403027202</v>
       </c>
@@ -14502,7 +14217,6 @@
       <c r="I364" t="s">
         <v>25</v>
       </c>
-      <c r="J364"/>
       <c r="O364" t="s">
         <v>652</v>
       </c>
@@ -14510,7 +14224,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="365" spans="1:20">
+    <row r="365" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B365" s="3">
         <v>417038601</v>
       </c>
@@ -14532,7 +14246,6 @@
       <c r="I365" t="s">
         <v>603</v>
       </c>
-      <c r="J365"/>
       <c r="O365" t="s">
         <v>652</v>
       </c>
@@ -14540,7 +14253,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="366" spans="1:20">
+    <row r="366" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B366" s="3">
         <v>420117202</v>
       </c>
@@ -14562,7 +14275,6 @@
       <c r="I366" t="s">
         <v>562</v>
       </c>
-      <c r="J366"/>
       <c r="O366" t="s">
         <v>652</v>
       </c>
@@ -14570,7 +14282,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="367" spans="1:20">
+    <row r="367" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B367" s="3">
         <v>103078600</v>
       </c>
@@ -14592,7 +14304,6 @@
       <c r="I367" t="s">
         <v>634</v>
       </c>
-      <c r="J367"/>
       <c r="O367" t="s">
         <v>652</v>
       </c>
@@ -14600,12 +14311,12 @@
         <v>653</v>
       </c>
     </row>
-    <row r="368" spans="1:20">
+    <row r="368" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B368" s="3">
         <v>415049105</v>
       </c>
-      <c r="C368" s="3">
-        <v>2747769670130402</v>
+      <c r="C368" s="3" t="s">
+        <v>718</v>
       </c>
       <c r="D368" t="s">
         <v>635</v>
@@ -14635,7 +14346,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="369" spans="1:20">
+    <row r="369" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B369" s="3">
         <v>419028603</v>
       </c>
@@ -14657,7 +14368,6 @@
       <c r="I369" t="s">
         <v>562</v>
       </c>
-      <c r="J369"/>
       <c r="O369" t="s">
         <v>652</v>
       </c>
@@ -14665,7 +14375,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="370" spans="1:20">
+    <row r="370" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B370" s="3">
         <v>409048607</v>
       </c>
@@ -14687,7 +14397,6 @@
       <c r="I370" t="s">
         <v>570</v>
       </c>
-      <c r="J370"/>
       <c r="O370" t="s">
         <v>652</v>
       </c>
@@ -14695,7 +14404,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="371" spans="1:20">
+    <row r="371" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B371" s="3">
         <v>15107601</v>
       </c>
@@ -14717,7 +14426,6 @@
       <c r="I371" t="s">
         <v>580</v>
       </c>
-      <c r="J371"/>
       <c r="O371" t="s">
         <v>652</v>
       </c>
@@ -14725,7 +14433,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="372" spans="1:20">
+    <row r="372" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B372" s="3">
         <v>420096903</v>
       </c>
@@ -14747,7 +14455,6 @@
       <c r="I372" t="s">
         <v>603</v>
       </c>
-      <c r="J372"/>
       <c r="O372" t="s">
         <v>652</v>
       </c>
@@ -14755,7 +14462,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="373" spans="1:20">
+    <row r="373" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B373" s="3">
         <v>405128601</v>
       </c>
@@ -14777,7 +14484,6 @@
       <c r="I373" t="s">
         <v>25</v>
       </c>
-      <c r="J373"/>
       <c r="O373" t="s">
         <v>652</v>
       </c>
@@ -14785,7 +14491,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="374" spans="1:20">
+    <row r="374" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B374" s="3">
         <v>429056701</v>
       </c>
@@ -14807,7 +14513,6 @@
       <c r="I374" t="s">
         <v>562</v>
       </c>
-      <c r="J374"/>
       <c r="O374" t="s">
         <v>652</v>
       </c>
@@ -14815,7 +14520,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="375" spans="1:20">
+    <row r="375" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B375" s="3">
         <v>417127902</v>
       </c>
@@ -14837,7 +14542,6 @@
       <c r="I375" t="s">
         <v>25</v>
       </c>
-      <c r="J375"/>
       <c r="O375" t="s">
         <v>652</v>
       </c>
@@ -14845,7 +14549,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="376" spans="1:20">
+    <row r="376" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B376" s="3">
         <v>413088004</v>
       </c>
@@ -14867,7 +14571,6 @@
       <c r="I376" t="s">
         <v>562</v>
       </c>
-      <c r="J376"/>
       <c r="O376" t="s">
         <v>652</v>
       </c>
@@ -14875,7 +14578,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="377" spans="1:20">
+    <row r="377" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B377" s="3">
         <v>420038901</v>
       </c>
@@ -14897,7 +14600,6 @@
       <c r="I377" t="s">
         <v>562</v>
       </c>
-      <c r="J377"/>
       <c r="O377" t="s">
         <v>652</v>
       </c>
@@ -14905,7 +14607,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="378" spans="1:20">
+    <row r="378" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B378" s="3">
         <v>412017503</v>
       </c>
@@ -14927,7 +14629,6 @@
       <c r="I378" t="s">
         <v>648</v>
       </c>
-      <c r="J378"/>
       <c r="O378" t="s">
         <v>652</v>
       </c>
@@ -14935,7 +14636,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="379" spans="1:20">
+    <row r="379" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B379" s="3">
         <v>418056801</v>
       </c>
@@ -14957,7 +14658,6 @@
       <c r="I379" t="s">
         <v>562</v>
       </c>
-      <c r="J379"/>
       <c r="O379" t="s">
         <v>652</v>
       </c>
@@ -14965,7 +14665,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="380" spans="1:20">
+    <row r="380" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B380" s="3">
         <v>409108602</v>
       </c>
@@ -14987,7 +14687,6 @@
       <c r="I380" t="s">
         <v>570</v>
       </c>
-      <c r="J380"/>
       <c r="O380" t="s">
         <v>652</v>
       </c>
@@ -14995,12 +14694,12 @@
         <v>653</v>
       </c>
     </row>
-    <row r="381" spans="1:20">
+    <row r="381" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B381" s="3">
         <v>12127410</v>
       </c>
-      <c r="C381" s="3">
-        <v>6544752653230163</v>
+      <c r="C381" s="3" t="s">
+        <v>709</v>
       </c>
       <c r="D381" t="s">
         <v>655</v>
@@ -15030,7 +14729,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="382" spans="1:20">
+    <row r="382" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B382" s="3">
         <v>416068101</v>
       </c>
@@ -15052,7 +14751,6 @@
       <c r="I382" t="s">
         <v>25</v>
       </c>
-      <c r="J382"/>
       <c r="O382" t="s">
         <v>652</v>
       </c>
@@ -15060,7 +14758,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" spans="1:20">
+    <row r="383" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B383" s="3">
         <v>406118803</v>
       </c>
@@ -15082,7 +14780,6 @@
       <c r="I383" t="s">
         <v>25</v>
       </c>
-      <c r="J383"/>
       <c r="O383" t="s">
         <v>652</v>
       </c>
@@ -15090,7 +14787,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="384" spans="1:20">
+    <row r="384" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B384" s="3">
         <v>415016301</v>
       </c>
@@ -15112,7 +14809,6 @@
       <c r="I384" t="s">
         <v>556</v>
       </c>
-      <c r="J384"/>
       <c r="M384" t="s">
         <v>551</v>
       </c>
@@ -15123,7 +14819,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="385" spans="1:20">
+    <row r="385" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B385" s="3">
         <v>324108103</v>
       </c>
@@ -15145,7 +14841,6 @@
       <c r="I385" t="s">
         <v>25</v>
       </c>
-      <c r="J385"/>
       <c r="M385" t="s">
         <v>551</v>
       </c>
@@ -15156,7 +14851,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="386" spans="1:20">
+    <row r="386" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B386" s="3">
         <v>406039002</v>
       </c>
@@ -15178,7 +14873,6 @@
       <c r="I386" t="s">
         <v>562</v>
       </c>
-      <c r="J386"/>
       <c r="M386" t="s">
         <v>551</v>
       </c>
@@ -15189,7 +14883,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="387" spans="1:20">
+    <row r="387" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B387" s="3">
         <v>409047703</v>
       </c>
@@ -15211,7 +14905,6 @@
       <c r="I387" t="s">
         <v>564</v>
       </c>
-      <c r="J387"/>
       <c r="M387" t="s">
         <v>551</v>
       </c>
@@ -15222,7 +14915,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="388" spans="1:20">
+    <row r="388" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B388" s="3">
         <v>427057407</v>
       </c>
@@ -15244,7 +14937,6 @@
       <c r="I388" t="s">
         <v>567</v>
       </c>
-      <c r="J388"/>
       <c r="M388" t="s">
         <v>551</v>
       </c>
@@ -15255,7 +14947,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="389" spans="1:20">
+    <row r="389" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B389" s="3">
         <v>428038302</v>
       </c>
@@ -15277,7 +14969,6 @@
       <c r="I389" t="s">
         <v>570</v>
       </c>
-      <c r="J389"/>
       <c r="M389" t="s">
         <v>551</v>
       </c>
@@ -15288,7 +14979,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="390" spans="1:20">
+    <row r="390" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B390" s="3">
         <v>406068904</v>
       </c>
@@ -15310,7 +15001,6 @@
       <c r="I390" t="s">
         <v>562</v>
       </c>
-      <c r="J390"/>
       <c r="M390" t="s">
         <v>551</v>
       </c>
@@ -15321,13 +15011,10 @@
         <v>551</v>
       </c>
     </row>
-    <row r="391" spans="1:20">
+    <row r="391" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B391" s="3">
         <v>2104066201</v>
       </c>
-      <c r="C391" s="3">
-        <v>0</v>
-      </c>
       <c r="D391" t="s">
         <v>197</v>
       </c>
@@ -15359,7 +15046,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="392" spans="1:20">
+    <row r="392" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B392" s="3">
         <v>307069501</v>
       </c>
@@ -15394,12 +15081,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="393" spans="1:20">
+    <row r="393" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B393" s="3">
         <v>416098301</v>
       </c>
-      <c r="C393" s="3">
-        <v>3248761661300003</v>
+      <c r="C393" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="D393" t="s">
         <v>578</v>
@@ -15419,7 +15106,6 @@
       <c r="I393" t="s">
         <v>580</v>
       </c>
-      <c r="J393"/>
       <c r="M393" t="s">
         <v>551</v>
       </c>
@@ -15430,13 +15116,10 @@
         <v>551</v>
       </c>
     </row>
-    <row r="394" spans="1:20">
+    <row r="394" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B394" s="3">
         <v>109118101</v>
       </c>
-      <c r="C394" s="3">
-        <v>0</v>
-      </c>
       <c r="D394" t="s">
         <v>581</v>
       </c>
@@ -15468,7 +15151,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="395" spans="1:20">
+    <row r="395" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B395" s="3">
         <v>607079301</v>
       </c>
@@ -15490,7 +15173,6 @@
       <c r="I395" t="s">
         <v>583</v>
       </c>
-      <c r="J395"/>
       <c r="M395" t="s">
         <v>551</v>
       </c>
@@ -15501,12 +15183,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="396" spans="1:20">
+    <row r="396" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B396" s="3">
         <v>428118601</v>
       </c>
-      <c r="C396" s="3">
-        <v>2460764665230233</v>
+      <c r="C396" s="3" t="s">
+        <v>711</v>
       </c>
       <c r="D396" t="s">
         <v>319</v>
@@ -15539,7 +15221,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="397" spans="1:20">
+    <row r="397" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B397" s="3">
         <v>402019003</v>
       </c>
@@ -15561,7 +15243,6 @@
       <c r="I397" t="s">
         <v>562</v>
       </c>
-      <c r="J397"/>
       <c r="M397" t="s">
         <v>551</v>
       </c>
@@ -15572,7 +15253,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="398" spans="1:20">
+    <row r="398" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B398" s="3">
         <v>416069101</v>
       </c>
@@ -15594,7 +15275,6 @@
       <c r="I398" t="s">
         <v>570</v>
       </c>
-      <c r="J398"/>
       <c r="M398" t="s">
         <v>551</v>
       </c>
@@ -15605,7 +15285,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="399" spans="1:20">
+    <row r="399" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B399" s="3">
         <v>429018903</v>
       </c>
@@ -15627,7 +15307,6 @@
       <c r="I399" t="s">
         <v>570</v>
       </c>
-      <c r="J399"/>
       <c r="M399" t="s">
         <v>551</v>
       </c>
@@ -15638,12 +15317,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="400" spans="1:20">
+    <row r="400" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B400" s="3">
         <v>313126401</v>
       </c>
-      <c r="C400" s="3">
-        <v>3674030312640003</v>
+      <c r="C400" s="3" t="s">
+        <v>712</v>
       </c>
       <c r="D400" t="s">
         <v>470</v>
@@ -15676,7 +15355,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="401" spans="1:20">
+    <row r="401" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B401" s="3">
         <v>320046101</v>
       </c>
@@ -15698,7 +15377,6 @@
       <c r="I401" t="s">
         <v>570</v>
       </c>
-      <c r="J401"/>
       <c r="M401" t="s">
         <v>551</v>
       </c>
@@ -15709,12 +15387,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="402" spans="1:20">
+    <row r="402" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B402" s="3">
         <v>418078701</v>
       </c>
-      <c r="C402" s="3">
-        <v>2050765666230343</v>
+      <c r="C402" s="3" t="s">
+        <v>713</v>
       </c>
       <c r="D402" t="s">
         <v>588</v>
@@ -15747,7 +15425,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="403" spans="1:20">
+    <row r="403" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B403" s="3">
         <v>603038002</v>
       </c>
@@ -15769,7 +15447,6 @@
       <c r="I403" t="s">
         <v>580</v>
       </c>
-      <c r="J403"/>
       <c r="M403" t="s">
         <v>551</v>
       </c>
@@ -15780,7 +15457,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="404" spans="1:20">
+    <row r="404" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B404" s="3">
         <v>415039101</v>
       </c>
@@ -15802,7 +15479,6 @@
       <c r="I404" t="s">
         <v>580</v>
       </c>
-      <c r="J404"/>
       <c r="M404" t="s">
         <v>551</v>
       </c>
@@ -15813,7 +15489,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="405" spans="1:20">
+    <row r="405" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B405" s="3">
         <v>401117901</v>
       </c>
@@ -15835,7 +15511,6 @@
       <c r="I405" t="s">
         <v>25</v>
       </c>
-      <c r="J405"/>
       <c r="M405" t="s">
         <v>551</v>
       </c>
@@ -15846,7 +15521,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="406" spans="1:20">
+    <row r="406" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B406" s="3">
         <v>419078903</v>
       </c>
@@ -15868,7 +15543,6 @@
       <c r="I406" t="s">
         <v>25</v>
       </c>
-      <c r="J406"/>
       <c r="M406" t="s">
         <v>551</v>
       </c>
@@ -15879,7 +15553,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="407" spans="1:20">
+    <row r="407" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B407" s="3">
         <v>430119102</v>
       </c>
@@ -15901,7 +15575,6 @@
       <c r="I407" t="s">
         <v>580</v>
       </c>
-      <c r="J407"/>
       <c r="M407" t="s">
         <v>551</v>
       </c>
@@ -15912,7 +15585,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="408" spans="1:20">
+    <row r="408" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B408" s="3">
         <v>428078803</v>
       </c>
@@ -15934,7 +15607,6 @@
       <c r="I408" t="s">
         <v>562</v>
       </c>
-      <c r="J408"/>
       <c r="M408" t="s">
         <v>551</v>
       </c>
@@ -15945,7 +15617,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="409" spans="1:20">
+    <row r="409" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B409" s="3">
         <v>415016301</v>
       </c>
@@ -15967,7 +15639,6 @@
       <c r="I409" t="s">
         <v>556</v>
       </c>
-      <c r="J409"/>
       <c r="M409" t="s">
         <v>551</v>
       </c>
@@ -15978,7 +15649,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="410" spans="1:20">
+    <row r="410" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B410" s="3">
         <v>324108103</v>
       </c>
@@ -16000,7 +15671,6 @@
       <c r="I410" t="s">
         <v>25</v>
       </c>
-      <c r="J410"/>
       <c r="M410" t="s">
         <v>551</v>
       </c>
@@ -16011,7 +15681,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="411" spans="1:20">
+    <row r="411" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B411" s="3">
         <v>406039002</v>
       </c>
@@ -16033,7 +15703,6 @@
       <c r="I411" t="s">
         <v>562</v>
       </c>
-      <c r="J411"/>
       <c r="M411" t="s">
         <v>551</v>
       </c>
@@ -16044,7 +15713,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="412" spans="1:20">
+    <row r="412" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B412" s="3">
         <v>409047703</v>
       </c>
@@ -16066,7 +15735,6 @@
       <c r="I412" t="s">
         <v>564</v>
       </c>
-      <c r="J412"/>
       <c r="M412" t="s">
         <v>551</v>
       </c>
@@ -16077,7 +15745,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="413" spans="1:20">
+    <row r="413" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B413" s="3">
         <v>427057407</v>
       </c>
@@ -16099,7 +15767,6 @@
       <c r="I413" t="s">
         <v>567</v>
       </c>
-      <c r="J413"/>
       <c r="M413" t="s">
         <v>551</v>
       </c>
@@ -16110,7 +15777,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="414" spans="1:20">
+    <row r="414" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B414" s="3">
         <v>428038302</v>
       </c>
@@ -16132,7 +15799,6 @@
       <c r="I414" t="s">
         <v>570</v>
       </c>
-      <c r="J414"/>
       <c r="M414" t="s">
         <v>551</v>
       </c>
@@ -16143,7 +15809,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="415" spans="1:20">
+    <row r="415" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B415" s="3">
         <v>406068904</v>
       </c>
@@ -16165,7 +15831,6 @@
       <c r="I415" t="s">
         <v>562</v>
       </c>
-      <c r="J415"/>
       <c r="M415" t="s">
         <v>551</v>
       </c>
@@ -16176,7 +15841,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="416" spans="1:20">
+    <row r="416" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B416" s="3">
         <v>307069501</v>
       </c>
@@ -16211,12 +15876,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="417" spans="1:20">
+    <row r="417" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B417" s="3">
         <v>416098301</v>
       </c>
-      <c r="C417" s="3">
-        <v>3248761661300003</v>
+      <c r="C417" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="D417" t="s">
         <v>578</v>
@@ -16236,7 +15901,6 @@
       <c r="I417" t="s">
         <v>580</v>
       </c>
-      <c r="J417"/>
       <c r="M417" t="s">
         <v>551</v>
       </c>
@@ -16247,13 +15911,10 @@
         <v>551</v>
       </c>
     </row>
-    <row r="418" spans="1:20">
+    <row r="418" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B418" s="3">
         <v>109118101</v>
       </c>
-      <c r="C418" s="3">
-        <v>0</v>
-      </c>
       <c r="D418" t="s">
         <v>581</v>
       </c>
@@ -16285,7 +15946,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="419" spans="1:20">
+    <row r="419" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B419" s="3">
         <v>607079301</v>
       </c>
@@ -16307,7 +15968,6 @@
       <c r="I419" t="s">
         <v>583</v>
       </c>
-      <c r="J419"/>
       <c r="M419" t="s">
         <v>551</v>
       </c>
@@ -16318,12 +15978,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="420" spans="1:20">
+    <row r="420" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B420" s="3">
         <v>428118601</v>
       </c>
-      <c r="C420" s="3">
-        <v>2460764665230233</v>
+      <c r="C420" s="3" t="s">
+        <v>711</v>
       </c>
       <c r="D420" t="s">
         <v>319</v>
@@ -16356,7 +16016,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="421" spans="1:20">
+    <row r="421" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B421" s="3">
         <v>402019003</v>
       </c>
@@ -16378,7 +16038,6 @@
       <c r="I421" t="s">
         <v>562</v>
       </c>
-      <c r="J421"/>
       <c r="M421" t="s">
         <v>551</v>
       </c>
@@ -16389,7 +16048,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="422" spans="1:20">
+    <row r="422" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B422" s="3">
         <v>416069101</v>
       </c>
@@ -16411,7 +16070,6 @@
       <c r="I422" t="s">
         <v>570</v>
       </c>
-      <c r="J422"/>
       <c r="M422" t="s">
         <v>551</v>
       </c>
@@ -16422,7 +16080,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="423" spans="1:20">
+    <row r="423" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B423" s="3">
         <v>429018903</v>
       </c>
@@ -16444,7 +16102,6 @@
       <c r="I423" t="s">
         <v>570</v>
       </c>
-      <c r="J423"/>
       <c r="M423" t="s">
         <v>551</v>
       </c>
@@ -16455,12 +16112,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="424" spans="1:20">
+    <row r="424" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B424" s="3">
         <v>313126401</v>
       </c>
-      <c r="C424" s="3">
-        <v>3674030312640003</v>
+      <c r="C424" s="3" t="s">
+        <v>712</v>
       </c>
       <c r="D424" t="s">
         <v>470</v>
@@ -16493,7 +16150,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="425" spans="1:20">
+    <row r="425" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B425" s="3">
         <v>320046101</v>
       </c>
@@ -16515,7 +16172,6 @@
       <c r="I425" t="s">
         <v>570</v>
       </c>
-      <c r="J425"/>
       <c r="M425" t="s">
         <v>551</v>
       </c>
@@ -16526,12 +16182,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="426" spans="1:20">
+    <row r="426" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B426" s="3">
         <v>418078701</v>
       </c>
-      <c r="C426" s="3">
-        <v>2050765666230343</v>
+      <c r="C426" s="3" t="s">
+        <v>713</v>
       </c>
       <c r="D426" t="s">
         <v>588</v>
@@ -16564,7 +16220,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="427" spans="1:20">
+    <row r="427" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B427" s="3">
         <v>603038002</v>
       </c>
@@ -16586,7 +16242,6 @@
       <c r="I427" t="s">
         <v>580</v>
       </c>
-      <c r="J427"/>
       <c r="M427" t="s">
         <v>551</v>
       </c>
@@ -16597,7 +16252,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="428" spans="1:20">
+    <row r="428" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B428" s="3">
         <v>415039101</v>
       </c>
@@ -16619,7 +16274,6 @@
       <c r="I428" t="s">
         <v>580</v>
       </c>
-      <c r="J428"/>
       <c r="M428" t="s">
         <v>551</v>
       </c>
@@ -16630,7 +16284,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="429" spans="1:20">
+    <row r="429" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B429" s="3">
         <v>401117901</v>
       </c>
@@ -16652,7 +16306,6 @@
       <c r="I429" t="s">
         <v>25</v>
       </c>
-      <c r="J429"/>
       <c r="M429" t="s">
         <v>551</v>
       </c>
@@ -16663,7 +16316,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="430" spans="1:20">
+    <row r="430" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B430" s="3">
         <v>419078903</v>
       </c>
@@ -16685,7 +16338,6 @@
       <c r="I430" t="s">
         <v>25</v>
       </c>
-      <c r="J430"/>
       <c r="M430" t="s">
         <v>551</v>
       </c>
@@ -16696,7 +16348,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="431" spans="1:20">
+    <row r="431" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B431" s="3">
         <v>430119102</v>
       </c>
@@ -16718,7 +16370,6 @@
       <c r="I431" t="s">
         <v>580</v>
       </c>
-      <c r="J431"/>
       <c r="M431" t="s">
         <v>551</v>
       </c>
@@ -16729,7 +16380,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="432" spans="1:20">
+    <row r="432" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B432" s="3">
         <v>428078803</v>
       </c>
@@ -16751,7 +16402,6 @@
       <c r="I432" t="s">
         <v>562</v>
       </c>
-      <c r="J432"/>
       <c r="M432" t="s">
         <v>551</v>
       </c>
@@ -16762,7 +16412,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="433" spans="1:20">
+    <row r="433" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B433" s="3">
         <v>628118902</v>
       </c>
@@ -16784,7 +16434,6 @@
       <c r="I433" t="s">
         <v>580</v>
       </c>
-      <c r="J433"/>
       <c r="M433" t="s">
         <v>551</v>
       </c>
@@ -16795,7 +16444,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="434" spans="1:20">
+    <row r="434" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B434" s="3">
         <v>420088503</v>
       </c>
@@ -16830,7 +16479,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="435" spans="1:20">
+    <row r="435" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B435" s="3">
         <v>428118904</v>
       </c>
@@ -16852,7 +16501,6 @@
       <c r="I435" t="s">
         <v>570</v>
       </c>
-      <c r="J435"/>
       <c r="M435" t="s">
         <v>551</v>
       </c>
@@ -16863,7 +16511,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="436" spans="1:20">
+    <row r="436" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B436" s="3">
         <v>415028303</v>
       </c>
@@ -16885,7 +16533,6 @@
       <c r="I436" t="s">
         <v>603</v>
       </c>
-      <c r="J436"/>
       <c r="M436" t="s">
         <v>551</v>
       </c>
@@ -16896,12 +16543,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="437" spans="1:20">
+    <row r="437" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B437" s="3">
         <v>2928037201</v>
       </c>
-      <c r="C437" s="3">
-        <v>6660750651130072</v>
+      <c r="C437" s="3" t="s">
+        <v>714</v>
       </c>
       <c r="D437" t="s">
         <v>604</v>
@@ -16934,7 +16581,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="438" spans="1:20">
+    <row r="438" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B438" s="3">
         <v>420087402</v>
       </c>
@@ -16956,7 +16603,6 @@
       <c r="I438" t="s">
         <v>570</v>
       </c>
-      <c r="J438"/>
       <c r="M438" t="s">
         <v>551</v>
       </c>
@@ -16967,7 +16613,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="439" spans="1:20">
+    <row r="439" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B439" s="3">
         <v>306046502</v>
       </c>
@@ -16989,7 +16635,6 @@
       <c r="I439" t="s">
         <v>25</v>
       </c>
-      <c r="J439"/>
       <c r="M439" t="s">
         <v>551</v>
       </c>
@@ -17000,7 +16645,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="440" spans="1:20">
+    <row r="440" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B440" s="3">
         <v>430079201</v>
       </c>
@@ -17022,7 +16667,6 @@
       <c r="I440" t="s">
         <v>564</v>
       </c>
-      <c r="J440"/>
       <c r="M440" t="s">
         <v>551</v>
       </c>
@@ -17033,7 +16677,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="441" spans="1:20">
+    <row r="441" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B441" s="3">
         <v>430068301</v>
       </c>
@@ -17055,7 +16699,6 @@
       <c r="I441" t="s">
         <v>562</v>
       </c>
-      <c r="J441"/>
       <c r="M441" t="s">
         <v>551</v>
       </c>
@@ -17066,7 +16709,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="442" spans="1:20">
+    <row r="442" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B442" s="3">
         <v>415016301</v>
       </c>
@@ -17088,7 +16731,6 @@
       <c r="I442" t="s">
         <v>556</v>
       </c>
-      <c r="J442"/>
       <c r="M442" t="s">
         <v>551</v>
       </c>
@@ -17099,7 +16741,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="443" spans="1:20">
+    <row r="443" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B443" s="3">
         <v>324108103</v>
       </c>
@@ -17121,7 +16763,6 @@
       <c r="I443" t="s">
         <v>25</v>
       </c>
-      <c r="J443"/>
       <c r="M443" t="s">
         <v>551</v>
       </c>
@@ -17132,7 +16773,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="444" spans="1:20">
+    <row r="444" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B444" s="3">
         <v>406039002</v>
       </c>
@@ -17154,7 +16795,6 @@
       <c r="I444" t="s">
         <v>562</v>
       </c>
-      <c r="J444"/>
       <c r="M444" t="s">
         <v>551</v>
       </c>
@@ -17165,7 +16805,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="445" spans="1:20">
+    <row r="445" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B445" s="3">
         <v>409047703</v>
       </c>
@@ -17187,7 +16827,6 @@
       <c r="I445" t="s">
         <v>564</v>
       </c>
-      <c r="J445"/>
       <c r="M445" t="s">
         <v>551</v>
       </c>
@@ -17198,7 +16837,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="446" spans="1:20">
+    <row r="446" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B446" s="3">
         <v>427057407</v>
       </c>
@@ -17220,7 +16859,6 @@
       <c r="I446" t="s">
         <v>567</v>
       </c>
-      <c r="J446"/>
       <c r="M446" t="s">
         <v>551</v>
       </c>
@@ -17231,7 +16869,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="447" spans="1:20">
+    <row r="447" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B447" s="3">
         <v>428038302</v>
       </c>
@@ -17253,7 +16891,6 @@
       <c r="I447" t="s">
         <v>570</v>
       </c>
-      <c r="J447"/>
       <c r="M447" t="s">
         <v>551</v>
       </c>
@@ -17264,7 +16901,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="448" spans="1:20">
+    <row r="448" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B448" s="3">
         <v>406068904</v>
       </c>
@@ -17286,7 +16923,6 @@
       <c r="I448" t="s">
         <v>562</v>
       </c>
-      <c r="J448"/>
       <c r="M448" t="s">
         <v>551</v>
       </c>
@@ -17297,12 +16933,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="449" spans="1:20">
+    <row r="449" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B449" s="3">
         <v>428118601</v>
       </c>
-      <c r="C449" s="3">
-        <v>2460764665230233</v>
+      <c r="C449" s="3" t="s">
+        <v>711</v>
       </c>
       <c r="D449" t="s">
         <v>319</v>
@@ -17335,7 +16971,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="450" spans="1:20">
+    <row r="450" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B450" s="3">
         <v>428078803</v>
       </c>
@@ -17357,7 +16993,6 @@
       <c r="I450" t="s">
         <v>562</v>
       </c>
-      <c r="J450"/>
       <c r="M450" t="s">
         <v>551</v>
       </c>
@@ -17368,7 +17003,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="451" spans="1:20">
+    <row r="451" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B451" s="3">
         <v>429019101</v>
       </c>
@@ -17390,7 +17025,6 @@
       <c r="I451" t="s">
         <v>583</v>
       </c>
-      <c r="J451"/>
       <c r="M451" t="s">
         <v>551</v>
       </c>
@@ -17401,7 +17035,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="452" spans="1:20">
+    <row r="452" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B452" s="3">
         <v>427048701</v>
       </c>
@@ -17423,7 +17057,6 @@
       <c r="I452" t="s">
         <v>25</v>
       </c>
-      <c r="J452"/>
       <c r="M452" t="s">
         <v>551</v>
       </c>
@@ -17434,7 +17067,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="453" spans="1:20">
+    <row r="453" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B453" s="3">
         <v>416119005</v>
       </c>
@@ -17456,7 +17089,6 @@
       <c r="I453" t="s">
         <v>583</v>
       </c>
-      <c r="J453"/>
       <c r="M453" t="s">
         <v>551</v>
       </c>
@@ -17467,7 +17099,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="454" spans="1:20">
+    <row r="454" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B454" s="3">
         <v>428069102</v>
       </c>
@@ -17489,7 +17121,6 @@
       <c r="I454" t="s">
         <v>562</v>
       </c>
-      <c r="J454"/>
       <c r="M454" t="s">
         <v>551</v>
       </c>
@@ -17500,7 +17131,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="455" spans="1:20">
+    <row r="455" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B455" s="3">
         <v>431088505</v>
       </c>
@@ -17522,7 +17153,6 @@
       <c r="I455" t="s">
         <v>25</v>
       </c>
-      <c r="J455"/>
       <c r="M455" t="s">
         <v>551</v>
       </c>
@@ -17533,7 +17163,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="456" spans="1:20">
+    <row r="456" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B456" s="3">
         <v>321066602</v>
       </c>
@@ -17568,7 +17198,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="457" spans="1:20">
+    <row r="457" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B457" s="3">
         <v>402018103</v>
       </c>
@@ -17590,7 +17220,6 @@
       <c r="I457" t="s">
         <v>673</v>
       </c>
-      <c r="J457"/>
       <c r="M457" t="s">
         <v>551</v>
       </c>
@@ -17601,7 +17230,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="458" spans="1:20">
+    <row r="458" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B458" s="3">
         <v>406078801</v>
       </c>
@@ -17623,7 +17252,6 @@
       <c r="I458" t="s">
         <v>562</v>
       </c>
-      <c r="J458"/>
       <c r="M458" t="s">
         <v>551</v>
       </c>
@@ -17634,7 +17262,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="459" spans="1:20">
+    <row r="459" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B459" s="3">
         <v>423016803</v>
       </c>
@@ -17656,7 +17284,6 @@
       <c r="I459" t="s">
         <v>562</v>
       </c>
-      <c r="J459"/>
       <c r="M459" t="s">
         <v>551</v>
       </c>
@@ -17667,7 +17294,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="460" spans="1:20">
+    <row r="460" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B460" s="3">
         <v>420058902</v>
       </c>
@@ -17689,7 +17316,6 @@
       <c r="I460" t="s">
         <v>562</v>
       </c>
-      <c r="J460"/>
       <c r="M460" t="s">
         <v>551</v>
       </c>
@@ -17700,7 +17326,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="461" spans="1:20">
+    <row r="461" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B461" s="3">
         <v>420097102</v>
       </c>
@@ -17722,7 +17348,6 @@
       <c r="I461" t="s">
         <v>562</v>
       </c>
-      <c r="J461"/>
       <c r="M461" t="s">
         <v>551</v>
       </c>
@@ -17733,7 +17358,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="462" spans="1:20">
+    <row r="462" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B462" s="3">
         <v>623058803</v>
       </c>
@@ -17755,7 +17380,6 @@
       <c r="I462" t="s">
         <v>580</v>
       </c>
-      <c r="J462"/>
       <c r="M462" t="s">
         <v>551</v>
       </c>
@@ -17766,7 +17390,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="463" spans="1:20">
+    <row r="463" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B463" s="3">
         <v>416108406</v>
       </c>
@@ -17788,7 +17412,6 @@
       <c r="I463" t="s">
         <v>570</v>
       </c>
-      <c r="J463"/>
       <c r="M463" t="s">
         <v>551</v>
       </c>
@@ -17799,13 +17422,10 @@
         <v>551</v>
       </c>
     </row>
-    <row r="464" spans="1:20">
+    <row r="464" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B464" s="3">
         <v>402087601</v>
       </c>
-      <c r="C464" s="3">
-        <v>402087601</v>
-      </c>
       <c r="D464" t="s">
         <v>681</v>
       </c>
@@ -17837,15 +17457,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="465" spans="1:20">
+    <row r="465" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B465" s="3">
         <v>431038701</v>
       </c>
-      <c r="C465" s="3" t="s">
+      <c r="D465" t="s">
         <v>683</v>
-      </c>
-      <c r="D465" t="s">
-        <v>684</v>
       </c>
       <c r="E465" t="s">
         <v>422</v>
@@ -17860,7 +17477,7 @@
         <v>24</v>
       </c>
       <c r="I465" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="J465" t="s">
         <v>670</v>
@@ -17875,12 +17492,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="466" spans="1:20">
+    <row r="466" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B466" s="3">
         <v>418108704</v>
       </c>
       <c r="D466" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E466" t="s">
         <v>89</v>
@@ -17897,7 +17514,6 @@
       <c r="I466" t="s">
         <v>562</v>
       </c>
-      <c r="J466"/>
       <c r="M466" t="s">
         <v>551</v>
       </c>
@@ -17908,12 +17524,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="467" spans="1:20">
+    <row r="467" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B467" s="3">
         <v>413068402</v>
       </c>
       <c r="D467" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E467" t="s">
         <v>31</v>
@@ -17930,7 +17546,6 @@
       <c r="I467" t="s">
         <v>562</v>
       </c>
-      <c r="J467"/>
       <c r="M467" t="s">
         <v>551</v>
       </c>
@@ -17941,15 +17556,15 @@
         <v>551</v>
       </c>
     </row>
-    <row r="468" spans="1:20">
+    <row r="468" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B468" s="3">
         <v>708069202</v>
       </c>
-      <c r="C468" s="3">
-        <v>6940770671230302</v>
+      <c r="C468" s="3" t="s">
+        <v>715</v>
       </c>
       <c r="D468" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E468" t="s">
         <v>592</v>
@@ -17979,12 +17594,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="469" spans="1:20">
+    <row r="469" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B469" s="3">
         <v>402088702</v>
       </c>
       <c r="D469" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E469" t="s">
         <v>89</v>
@@ -17999,9 +17614,8 @@
         <v>555</v>
       </c>
       <c r="I469" t="s">
-        <v>690</v>
-      </c>
-      <c r="J469"/>
+        <v>689</v>
+      </c>
       <c r="M469" t="s">
         <v>551</v>
       </c>
@@ -18012,7 +17626,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="470" spans="1:20">
+    <row r="470" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B470" s="3">
         <v>420058301</v>
       </c>
@@ -18034,7 +17648,6 @@
       <c r="I470" t="s">
         <v>570</v>
       </c>
-      <c r="J470"/>
       <c r="M470" t="s">
         <v>551</v>
       </c>
@@ -18045,12 +17658,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="471" spans="1:20">
+    <row r="471" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B471" s="3">
         <v>404118802</v>
       </c>
       <c r="D471" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E471" t="s">
         <v>661</v>
@@ -18067,7 +17680,6 @@
       <c r="I471" t="s">
         <v>25</v>
       </c>
-      <c r="J471"/>
       <c r="M471" t="s">
         <v>551</v>
       </c>
@@ -18078,18 +17690,18 @@
         <v>551</v>
       </c>
     </row>
-    <row r="472" spans="1:20">
+    <row r="472" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B472" s="3">
         <v>409078002</v>
       </c>
-      <c r="C472" s="3">
-        <v>4041758659130173</v>
+      <c r="C472" s="3" t="s">
+        <v>716</v>
       </c>
       <c r="D472" t="s">
+        <v>691</v>
+      </c>
+      <c r="E472" t="s">
         <v>692</v>
-      </c>
-      <c r="E472" t="s">
-        <v>693</v>
       </c>
       <c r="F472" s="3">
         <v>41009</v>
@@ -18101,7 +17713,7 @@
         <v>24</v>
       </c>
       <c r="I472" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J472" t="s">
         <v>670</v>
@@ -18116,12 +17728,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="473" spans="1:20">
+    <row r="473" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B473" s="3">
         <v>430058502</v>
       </c>
       <c r="D473" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E473" t="s">
         <v>625</v>
@@ -18138,7 +17750,6 @@
       <c r="I473" t="s">
         <v>562</v>
       </c>
-      <c r="J473"/>
       <c r="M473" t="s">
         <v>551</v>
       </c>
@@ -18149,15 +17760,15 @@
         <v>551</v>
       </c>
     </row>
-    <row r="474" spans="1:20">
+    <row r="474" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B474" s="3">
         <v>721068802</v>
       </c>
-      <c r="C474" s="3">
-        <v>2953766667130260</v>
+      <c r="C474" s="3" t="s">
+        <v>717</v>
       </c>
       <c r="D474" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E474" t="s">
         <v>592</v>
@@ -18187,7 +17798,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="475" spans="1:20">
+    <row r="475" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B475" s="3">
         <v>411038901</v>
       </c>
@@ -18209,7 +17820,6 @@
       <c r="I475" t="s">
         <v>562</v>
       </c>
-      <c r="J475"/>
       <c r="M475" t="s">
         <v>551</v>
       </c>
@@ -18220,15 +17830,15 @@
         <v>551</v>
       </c>
     </row>
-    <row r="476" spans="1:20">
+    <row r="476" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B476" s="3">
         <v>422118003</v>
       </c>
       <c r="D476" t="s">
+        <v>696</v>
+      </c>
+      <c r="E476" t="s">
         <v>697</v>
-      </c>
-      <c r="E476" t="s">
-        <v>698</v>
       </c>
       <c r="F476" s="3">
         <v>43214</v>
@@ -18240,9 +17850,8 @@
         <v>24</v>
       </c>
       <c r="I476" t="s">
-        <v>699</v>
-      </c>
-      <c r="J476"/>
+        <v>698</v>
+      </c>
       <c r="M476" t="s">
         <v>551</v>
       </c>
@@ -18253,12 +17862,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="477" spans="1:20">
+    <row r="477" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B477" s="3">
         <v>405018902</v>
       </c>
       <c r="D477" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E477" t="s">
         <v>661</v>
@@ -18275,7 +17884,6 @@
       <c r="I477" t="s">
         <v>25</v>
       </c>
-      <c r="J477"/>
       <c r="M477" t="s">
         <v>551</v>
       </c>
@@ -18286,12 +17894,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="478" spans="1:20">
+    <row r="478" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B478" s="3">
         <v>307067601</v>
       </c>
       <c r="D478" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E478" t="s">
         <v>312</v>
@@ -18308,7 +17916,6 @@
       <c r="I478" t="s">
         <v>570</v>
       </c>
-      <c r="J478"/>
       <c r="M478" t="s">
         <v>551</v>
       </c>
@@ -18319,12 +17926,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="479" spans="1:20">
+    <row r="479" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B479" s="3">
         <v>401088701</v>
       </c>
       <c r="D479" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E479" t="s">
         <v>89</v>
@@ -18341,7 +17948,6 @@
       <c r="I479" t="s">
         <v>562</v>
       </c>
-      <c r="J479"/>
       <c r="M479" t="s">
         <v>551</v>
       </c>
@@ -18352,12 +17958,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="480" spans="1:20">
+    <row r="480" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B480" s="3">
         <v>414106203</v>
       </c>
       <c r="D480" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E480" t="s">
         <v>672</v>
@@ -18374,7 +17980,6 @@
       <c r="I480" t="s">
         <v>25</v>
       </c>
-      <c r="J480"/>
       <c r="M480" t="s">
         <v>551</v>
       </c>
@@ -18385,12 +17990,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="481" spans="1:20">
+    <row r="481" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B481" s="3">
         <v>402016904</v>
       </c>
       <c r="D481" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E481" t="s">
         <v>554</v>
@@ -18405,9 +18010,8 @@
         <v>555</v>
       </c>
       <c r="I481" t="s">
-        <v>690</v>
-      </c>
-      <c r="J481"/>
+        <v>689</v>
+      </c>
       <c r="M481" t="s">
         <v>551</v>
       </c>
@@ -18418,12 +18022,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="482" spans="1:20">
+    <row r="482" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B482" s="3">
         <v>727048809</v>
       </c>
       <c r="D482" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E482" t="s">
         <v>592</v>
@@ -18440,7 +18044,6 @@
       <c r="I482" t="s">
         <v>580</v>
       </c>
-      <c r="J482"/>
       <c r="M482" t="s">
         <v>551</v>
       </c>
@@ -18451,7 +18054,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="483" spans="1:20">
+    <row r="483" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B483" s="3">
         <v>429038403</v>
       </c>
@@ -18459,10 +18062,10 @@
         <v>25</v>
       </c>
       <c r="D483" t="s">
+        <v>705</v>
+      </c>
+      <c r="E483" t="s">
         <v>706</v>
-      </c>
-      <c r="E483" t="s">
-        <v>707</v>
       </c>
       <c r="F483" s="3">
         <v>43377</v>
@@ -18474,7 +18077,7 @@
         <v>555</v>
       </c>
       <c r="I483" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="J483" t="s">
         <v>577</v>
@@ -18489,7 +18092,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="484" spans="1:20">
+    <row r="484" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B484" s="3">
         <v>429019101</v>
       </c>
@@ -18511,18 +18114,17 @@
       <c r="I484" t="s">
         <v>583</v>
       </c>
-      <c r="J484"/>
       <c r="M484" t="s">
         <v>551</v>
       </c>
       <c r="O484" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P484" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="485" spans="1:20">
+    <row r="485" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B485" s="3">
         <v>427048701</v>
       </c>
@@ -18544,18 +18146,17 @@
       <c r="I485" t="s">
         <v>25</v>
       </c>
-      <c r="J485"/>
       <c r="M485" t="s">
         <v>551</v>
       </c>
       <c r="O485" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P485" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="486" spans="1:20">
+    <row r="486" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B486" s="3">
         <v>416119005</v>
       </c>
@@ -18577,18 +18178,17 @@
       <c r="I486" t="s">
         <v>583</v>
       </c>
-      <c r="J486"/>
       <c r="M486" t="s">
         <v>551</v>
       </c>
       <c r="O486" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P486" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="487" spans="1:20">
+    <row r="487" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B487" s="3">
         <v>428069102</v>
       </c>
@@ -18610,18 +18210,17 @@
       <c r="I487" t="s">
         <v>562</v>
       </c>
-      <c r="J487"/>
       <c r="M487" t="s">
         <v>551</v>
       </c>
       <c r="O487" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P487" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="488" spans="1:20">
+    <row r="488" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B488" s="3">
         <v>431088505</v>
       </c>
@@ -18643,18 +18242,17 @@
       <c r="I488" t="s">
         <v>25</v>
       </c>
-      <c r="J488"/>
       <c r="M488" t="s">
         <v>551</v>
       </c>
       <c r="O488" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P488" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="489" spans="1:20">
+    <row r="489" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B489" s="3">
         <v>321066602</v>
       </c>
@@ -18683,13 +18281,13 @@
         <v>551</v>
       </c>
       <c r="O489" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P489" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="490" spans="1:20">
+    <row r="490" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B490" s="3">
         <v>402018103</v>
       </c>
@@ -18711,18 +18309,17 @@
       <c r="I490" t="s">
         <v>673</v>
       </c>
-      <c r="J490"/>
       <c r="M490" t="s">
         <v>551</v>
       </c>
       <c r="O490" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P490" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="491" spans="1:20">
+    <row r="491" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B491" s="3">
         <v>406078801</v>
       </c>
@@ -18744,18 +18341,17 @@
       <c r="I491" t="s">
         <v>562</v>
       </c>
-      <c r="J491"/>
       <c r="M491" t="s">
         <v>551</v>
       </c>
       <c r="O491" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P491" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="492" spans="1:20">
+    <row r="492" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B492" s="3">
         <v>423016803</v>
       </c>
@@ -18777,18 +18373,17 @@
       <c r="I492" t="s">
         <v>562</v>
       </c>
-      <c r="J492"/>
       <c r="M492" t="s">
         <v>551</v>
       </c>
       <c r="O492" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P492" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="493" spans="1:20">
+    <row r="493" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B493" s="3">
         <v>420058902</v>
       </c>
@@ -18810,29 +18405,18 @@
       <c r="I493" t="s">
         <v>562</v>
       </c>
-      <c r="J493"/>
       <c r="M493" t="s">
         <v>551</v>
       </c>
       <c r="O493" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P493" t="s">
         <v>551</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <autoFilter ref="A1:R493" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>